--- a/research/traditional_assets/database/data/belgium/belgium_heathcare_information_and_technology.xlsx
+++ b/research/traditional_assets/database/data/belgium/belgium_heathcare_information_and_technology.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="earnings_debt" sheetId="1" r:id="rId1"/>
+    <sheet name="cost_capital" sheetId="2" r:id="rId2"/>
+    <sheet name="enxtbr_agfb" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -588,34 +590,34 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.0558</v>
+        <v>-0.04</v>
       </c>
       <c r="G2">
-        <v>0.07685526968211118</v>
+        <v>0.05851063829787234</v>
       </c>
       <c r="H2">
-        <v>0.02446146217839238</v>
+        <v>0.006484295845997974</v>
       </c>
       <c r="I2">
-        <v>-0.01515068040328357</v>
+        <v>0.0005369807497467073</v>
       </c>
       <c r="J2">
-        <v>-0.01515068040328357</v>
+        <v>0.0005369807497467073</v>
       </c>
       <c r="K2">
-        <v>-59.8</v>
+        <v>-295.3</v>
       </c>
       <c r="L2">
-        <v>-0.03294584320423117</v>
+        <v>-0.1495947315096251</v>
       </c>
       <c r="M2">
-        <v>28.4</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.06428248076052512</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>-0.4749163879598662</v>
+        <v>-0</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -627,79 +629,76 @@
         <v>-0</v>
       </c>
       <c r="S2">
-        <v>28.4</v>
-      </c>
-      <c r="T2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U2">
-        <v>174.5</v>
+        <v>57.2</v>
       </c>
       <c r="V2">
-        <v>0.3949751018560435</v>
+        <v>0.2273449920508744</v>
       </c>
       <c r="W2">
-        <v>-0.08024691358024691</v>
+        <v>-0.4131225517627309</v>
       </c>
       <c r="X2">
-        <v>0.1390986395106163</v>
+        <v>0.120751746319344</v>
       </c>
       <c r="Y2">
-        <v>-0.2193455530908632</v>
+        <v>-0.5338742980820749</v>
       </c>
       <c r="Z2">
-        <v>36.52112676056331</v>
+        <v>6.270648030495554</v>
       </c>
       <c r="AA2">
-        <v>-0.5533199195171015</v>
+        <v>0.003367217280813216</v>
       </c>
       <c r="AB2">
-        <v>0.1244548244130002</v>
+        <v>0.09875927720252529</v>
       </c>
       <c r="AC2">
-        <v>-0.6777747439301017</v>
+        <v>-0.09539205992171208</v>
       </c>
       <c r="AD2">
-        <v>77.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>77.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="AG2">
-        <v>-97</v>
+        <v>34.89999999999999</v>
       </c>
       <c r="AH2">
-        <v>0.1492393606778356</v>
+        <v>0.2679662496363107</v>
       </c>
       <c r="AI2">
-        <v>0.09179201705554899</v>
+        <v>0.1702717692734332</v>
       </c>
       <c r="AJ2">
-        <v>-0.281322505800464</v>
+        <v>0.1218150087260035</v>
       </c>
       <c r="AK2">
-        <v>-0.1448193490594207</v>
+        <v>0.0721521604300186</v>
       </c>
       <c r="AL2">
-        <v>4.9</v>
+        <v>18</v>
       </c>
       <c r="AM2">
-        <v>-3.93</v>
+        <v>-2.100000000000001</v>
       </c>
       <c r="AN2">
-        <v>26.36054421768707</v>
+        <v>3.349090909090909</v>
       </c>
       <c r="AO2">
-        <v>-5.612244897959183</v>
+        <v>0.05888888888888889</v>
       </c>
       <c r="AP2">
-        <v>-32.99319727891157</v>
+        <v>1.269090909090909</v>
       </c>
       <c r="AQ2">
-        <v>6.997455470737914</v>
+        <v>-0.5047619047619044</v>
       </c>
     </row>
     <row r="3">
@@ -719,34 +718,34 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.0558</v>
+        <v>-0.04</v>
       </c>
       <c r="G3">
-        <v>0.07685526968211118</v>
+        <v>0.05851063829787234</v>
       </c>
       <c r="H3">
-        <v>0.02446146217839238</v>
+        <v>0.006484295845997974</v>
       </c>
       <c r="I3">
-        <v>-0.01515068040328357</v>
+        <v>0.0005369807497467073</v>
       </c>
       <c r="J3">
-        <v>-0.01515068040328357</v>
+        <v>0.0005369807497467073</v>
       </c>
       <c r="K3">
-        <v>-59.8</v>
+        <v>-295.3</v>
       </c>
       <c r="L3">
-        <v>-0.03294584320423117</v>
+        <v>-0.1495947315096251</v>
       </c>
       <c r="M3">
-        <v>28.4</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.06428248076052512</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>-0.4749163879598662</v>
+        <v>0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,79 +757,8848 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>28.4</v>
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <v>57.2</v>
+      </c>
+      <c r="V3">
+        <v>0.2273449920508744</v>
+      </c>
+      <c r="W3">
+        <v>-0.4131225517627309</v>
+      </c>
+      <c r="X3">
+        <v>0.120751746319344</v>
+      </c>
+      <c r="Y3">
+        <v>-0.5338742980820749</v>
+      </c>
+      <c r="Z3">
+        <v>6.270648030495554</v>
+      </c>
+      <c r="AA3">
+        <v>0.003367217280813216</v>
+      </c>
+      <c r="AB3">
+        <v>0.09875927720252529</v>
+      </c>
+      <c r="AC3">
+        <v>-0.09539205992171208</v>
+      </c>
+      <c r="AD3">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AE3">
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AG3">
+        <v>34.89999999999999</v>
+      </c>
+      <c r="AH3">
+        <v>0.2679662496363107</v>
+      </c>
+      <c r="AI3">
+        <v>0.1702717692734332</v>
+      </c>
+      <c r="AJ3">
+        <v>0.1218150087260035</v>
+      </c>
+      <c r="AK3">
+        <v>0.0721521604300186</v>
+      </c>
+      <c r="AL3">
+        <v>18</v>
+      </c>
+      <c r="AM3">
+        <v>-2.100000000000001</v>
+      </c>
+      <c r="AN3">
+        <v>3.349090909090909</v>
+      </c>
+      <c r="AO3">
+        <v>0.05888888888888889</v>
+      </c>
+      <c r="AP3">
+        <v>1.269090909090909</v>
+      </c>
+      <c r="AQ3">
+        <v>-0.5047619047619044</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AY2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>company_name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>exchange_ticker</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>industry_group</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>country</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>current_interest_coverage</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_interest_coverage</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_ebitda</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_capital</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_capital</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>current_equity_value</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_equity_value</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>current_enterprise_value</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_enterprise_value</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_capital</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_capital</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>current_debt_rating</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_debt_rating</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>current_cost_equity</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_cost_equity</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>current_beta</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>optimal_beta</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_mv_debt</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_coverage_ratio</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_debt</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_interest_expense</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_depreciation</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>adjusted_ebitda</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>country_default_spread</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>risk_free</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>market_capitalization</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_risk_premium</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>reported_debt_rating</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>marginal_tax_rate</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_max_percentage</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>deductions_method</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_drop_ebitda</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>reported_capital_spending</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>reported_interest_expense</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>reported_bv_debt</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>reported_cash</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>estimated_ev_implied_growth</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>flag_bankruptcy</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>flag_refinanced</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>rating_firm_type</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio_limit</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Agfa-Gevaert NV (ENXTBR:AGFB)</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ENXTBR:AGFB</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Heathcare Information and Technology</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="E2">
+        <v>0.0588888888888888</v>
+      </c>
+      <c r="F2">
+        <v>4.53480260937877</v>
+      </c>
+      <c r="G2">
+        <v>3.34909090909091</v>
+      </c>
+      <c r="H2">
+        <v>4.49934545454545</v>
+      </c>
+      <c r="I2">
+        <v>0.267966249636311</v>
+      </c>
+      <c r="J2">
+        <v>0.36</v>
+      </c>
+      <c r="K2">
+        <v>251.6</v>
+      </c>
+      <c r="L2">
+        <v>228.187665973149</v>
+      </c>
+      <c r="M2">
+        <v>286.5</v>
+      </c>
+      <c r="N2">
+        <v>294.719665973149</v>
+      </c>
+      <c r="O2">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="P2">
+        <v>123.732</v>
+      </c>
+      <c r="Q2">
+        <v>0.09875927720252529</v>
+      </c>
+      <c r="R2">
+        <v>0.0970870262892078</v>
+      </c>
+      <c r="S2">
+        <v>0.0386799587465906</v>
+      </c>
+      <c r="T2">
+        <v>0.038175</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="W2">
+        <v>0.120751746319344</v>
+      </c>
+      <c r="X2">
+        <v>0.130225041076887</v>
+      </c>
+      <c r="Y2">
+        <v>1.49638447082143</v>
+      </c>
+      <c r="Z2">
+        <v>1.66936054270967</v>
+      </c>
+      <c r="AA2">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AB2">
+        <v>0.0515732783287875</v>
+      </c>
+      <c r="AC2">
+        <v>0.05888888888888882</v>
+      </c>
+      <c r="AD2">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AE2">
+        <v>18</v>
+      </c>
+      <c r="AF2">
+        <v>26.44</v>
+      </c>
+      <c r="AG2">
+        <v>27.5</v>
+      </c>
+      <c r="AH2">
+        <v>0</v>
+      </c>
+      <c r="AI2">
+        <v>0.0388</v>
+      </c>
+      <c r="AJ2">
+        <v>251.6</v>
+      </c>
+      <c r="AK2">
+        <v>0.05476650414205181</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="AM2">
+        <v>0.25</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+      <c r="AO2">
+        <v>2</v>
+      </c>
+      <c r="AQ2">
+        <v>49.76000000000001</v>
+      </c>
+      <c r="AR2">
+        <v>18</v>
+      </c>
+      <c r="AS2">
+        <v>92.09999999999999</v>
+      </c>
+      <c r="AT2">
+        <v>57.2</v>
+      </c>
+      <c r="AV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="AW2" t="b">
+        <v>1</v>
+      </c>
+      <c r="AX2">
+        <v>1</v>
+      </c>
+      <c r="AY2">
+        <v>10000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Z101"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>debt_capital</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>cost_capital</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>equity_value</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>debt_issued</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>debt</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>cash</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>marketcap</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>drop_ebitda</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>depreciation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ebit</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>interest_expense</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>taxable_income</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>taxes</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>net_income</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>operating_cash_flow</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>debt_equity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>cost_equity</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>beta</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_pre_tax</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>tax_rate</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>cost_debt_after_tax</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>debt_rating</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_ratio</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>coverage_error</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2">
+        <v>0</v>
+      </c>
+      <c r="B2">
+        <v>0.1030989299881405</v>
+      </c>
+      <c r="C2">
+        <v>324.3635892182332</v>
+      </c>
+      <c r="D2">
+        <v>267.1635892182333</v>
+      </c>
+      <c r="E2">
+        <v>-92.09999999999999</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>57.2</v>
+      </c>
+      <c r="H2">
+        <v>251.6</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>55</v>
+      </c>
+      <c r="K2">
+        <v>26.44</v>
+      </c>
+      <c r="L2">
+        <v>28.56</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>28.56</v>
+      </c>
+      <c r="O2">
+        <v>7.14</v>
+      </c>
+      <c r="P2">
+        <v>21.42</v>
+      </c>
+      <c r="Q2">
+        <v>47.86</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>0.1030989299881405</v>
+      </c>
+      <c r="T2">
+        <v>1.174055766301309</v>
+      </c>
+      <c r="U2">
+        <v>0.0447</v>
+      </c>
+      <c r="V2">
+        <v>0.25</v>
+      </c>
+      <c r="W2">
+        <v>0.033525</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y2">
+        <v>10000000</v>
+      </c>
+      <c r="Z2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3">
+        <v>0.01</v>
+      </c>
+      <c r="B3">
+        <v>0.1028854326631701</v>
+      </c>
+      <c r="C3">
+        <v>321.8166309836897</v>
+      </c>
+      <c r="D3">
+        <v>268.0536309836897</v>
+      </c>
+      <c r="E3">
+        <v>-88.663</v>
+      </c>
+      <c r="F3">
+        <v>3.437</v>
+      </c>
+      <c r="G3">
+        <v>57.2</v>
+      </c>
+      <c r="H3">
+        <v>251.6</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <v>55</v>
+      </c>
+      <c r="K3">
+        <v>26.44</v>
+      </c>
+      <c r="L3">
+        <v>28.56</v>
+      </c>
+      <c r="M3">
+        <v>0.1536339</v>
+      </c>
+      <c r="N3">
+        <v>28.4063661</v>
+      </c>
+      <c r="O3">
+        <v>7.101591525</v>
+      </c>
+      <c r="P3">
+        <v>21.304774575</v>
+      </c>
+      <c r="Q3">
+        <v>47.744774575</v>
+      </c>
+      <c r="R3">
+        <v>0.0101010101010101</v>
+      </c>
+      <c r="S3">
+        <v>0.1035860430941112</v>
       </c>
       <c r="T3">
+        <v>1.182950128167228</v>
+      </c>
+      <c r="U3">
+        <v>0.0447</v>
+      </c>
+      <c r="V3">
+        <v>0.25</v>
+      </c>
+      <c r="W3">
+        <v>0.033525</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y3">
+        <v>185.8964720676882</v>
+      </c>
+      <c r="Z3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4">
+        <v>0.02</v>
+      </c>
+      <c r="B4">
+        <v>0.1026719353381998</v>
+      </c>
+      <c r="C4">
+        <v>319.2756228283172</v>
+      </c>
+      <c r="D4">
+        <v>268.9496228283173</v>
+      </c>
+      <c r="E4">
+        <v>-85.226</v>
+      </c>
+      <c r="F4">
+        <v>6.874</v>
+      </c>
+      <c r="G4">
+        <v>57.2</v>
+      </c>
+      <c r="H4">
+        <v>251.6</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>55</v>
+      </c>
+      <c r="K4">
+        <v>26.44</v>
+      </c>
+      <c r="L4">
+        <v>28.56</v>
+      </c>
+      <c r="M4">
+        <v>0.3072678</v>
+      </c>
+      <c r="N4">
+        <v>28.2527322</v>
+      </c>
+      <c r="O4">
+        <v>7.063183049999999</v>
+      </c>
+      <c r="P4">
+        <v>21.18954915</v>
+      </c>
+      <c r="Q4">
+        <v>47.62954915</v>
+      </c>
+      <c r="R4">
+        <v>0.02040816326530612</v>
+      </c>
+      <c r="S4">
+        <v>0.1040830972838773</v>
+      </c>
+      <c r="T4">
+        <v>1.192026007622248</v>
+      </c>
+      <c r="U4">
+        <v>0.0447</v>
+      </c>
+      <c r="V4">
+        <v>0.25</v>
+      </c>
+      <c r="W4">
+        <v>0.033525</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y4">
+        <v>92.94823603384407</v>
+      </c>
+      <c r="Z4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5">
+        <v>0.03</v>
+      </c>
+      <c r="B5">
+        <v>0.1024584380132294</v>
+      </c>
+      <c r="C5">
+        <v>316.740624618146</v>
+      </c>
+      <c r="D5">
+        <v>269.851624618146</v>
+      </c>
+      <c r="E5">
+        <v>-81.78899999999999</v>
+      </c>
+      <c r="F5">
+        <v>10.311</v>
+      </c>
+      <c r="G5">
+        <v>57.2</v>
+      </c>
+      <c r="H5">
+        <v>251.6</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>55</v>
+      </c>
+      <c r="K5">
+        <v>26.44</v>
+      </c>
+      <c r="L5">
+        <v>28.56</v>
+      </c>
+      <c r="M5">
+        <v>0.4609017</v>
+      </c>
+      <c r="N5">
+        <v>28.0990983</v>
+      </c>
+      <c r="O5">
+        <v>7.024774574999999</v>
+      </c>
+      <c r="P5">
+        <v>21.074323725</v>
+      </c>
+      <c r="Q5">
+        <v>47.514323725</v>
+      </c>
+      <c r="R5">
+        <v>0.03092783505154639</v>
+      </c>
+      <c r="S5">
+        <v>0.1045904000136386</v>
+      </c>
+      <c r="T5">
+        <v>1.201289018612422</v>
+      </c>
+      <c r="U5">
+        <v>0.0447</v>
+      </c>
+      <c r="V5">
+        <v>0.25</v>
+      </c>
+      <c r="W5">
+        <v>0.033525</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y5">
+        <v>61.96549068922939</v>
+      </c>
+      <c r="Z5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6">
+        <v>0.04</v>
+      </c>
+      <c r="B6">
+        <v>0.1022449406882591</v>
+      </c>
+      <c r="C6">
+        <v>314.2116970250217</v>
+      </c>
+      <c r="D6">
+        <v>270.7596970250218</v>
+      </c>
+      <c r="E6">
+        <v>-78.35199999999999</v>
+      </c>
+      <c r="F6">
+        <v>13.748</v>
+      </c>
+      <c r="G6">
+        <v>57.2</v>
+      </c>
+      <c r="H6">
+        <v>251.6</v>
+      </c>
+      <c r="I6">
+        <v>0</v>
+      </c>
+      <c r="J6">
+        <v>55</v>
+      </c>
+      <c r="K6">
+        <v>26.44</v>
+      </c>
+      <c r="L6">
+        <v>28.56</v>
+      </c>
+      <c r="M6">
+        <v>0.6145356000000001</v>
+      </c>
+      <c r="N6">
+        <v>27.9454644</v>
+      </c>
+      <c r="O6">
+        <v>6.9863661</v>
+      </c>
+      <c r="P6">
+        <v>20.9590983</v>
+      </c>
+      <c r="Q6">
+        <v>47.39909830000001</v>
+      </c>
+      <c r="R6">
+        <v>0.04166666666666667</v>
+      </c>
+      <c r="S6">
+        <v>0.1051082715502699</v>
+      </c>
+      <c r="T6">
+        <v>1.210745008998225</v>
+      </c>
+      <c r="U6">
+        <v>0.0447</v>
+      </c>
+      <c r="V6">
+        <v>0.25</v>
+      </c>
+      <c r="W6">
+        <v>0.033525</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y6">
+        <v>46.47411801692204</v>
+      </c>
+      <c r="Z6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7">
+        <v>0.05</v>
+      </c>
+      <c r="B7">
+        <v>0.1020314433632887</v>
+      </c>
+      <c r="C7">
+        <v>311.6889015402105</v>
+      </c>
+      <c r="D7">
+        <v>271.6739015402105</v>
+      </c>
+      <c r="E7">
+        <v>-74.91499999999999</v>
+      </c>
+      <c r="F7">
+        <v>17.185</v>
+      </c>
+      <c r="G7">
+        <v>57.2</v>
+      </c>
+      <c r="H7">
+        <v>251.6</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>55</v>
+      </c>
+      <c r="K7">
+        <v>26.44</v>
+      </c>
+      <c r="L7">
+        <v>28.56</v>
+      </c>
+      <c r="M7">
+        <v>0.7681694999999999</v>
+      </c>
+      <c r="N7">
+        <v>27.7918305</v>
+      </c>
+      <c r="O7">
+        <v>6.947957625</v>
+      </c>
+      <c r="P7">
+        <v>20.843872875</v>
+      </c>
+      <c r="Q7">
+        <v>47.283872875</v>
+      </c>
+      <c r="R7">
+        <v>0.05263157894736843</v>
+      </c>
+      <c r="S7">
+        <v>0.1056370456455671</v>
+      </c>
+      <c r="T7">
+        <v>1.220400072865835</v>
+      </c>
+      <c r="U7">
+        <v>0.0447</v>
+      </c>
+      <c r="V7">
+        <v>0.25</v>
+      </c>
+      <c r="W7">
+        <v>0.033525</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y7">
+        <v>37.17929441353764</v>
+      </c>
+      <c r="Z7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8">
+        <v>0.06</v>
+      </c>
+      <c r="B8">
+        <v>0.1018179460383184</v>
+      </c>
+      <c r="C8">
+        <v>309.1723004882788</v>
+      </c>
+      <c r="D8">
+        <v>272.5943004882789</v>
+      </c>
+      <c r="E8">
+        <v>-71.47799999999999</v>
+      </c>
+      <c r="F8">
+        <v>20.622</v>
+      </c>
+      <c r="G8">
+        <v>57.2</v>
+      </c>
+      <c r="H8">
+        <v>251.6</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>55</v>
+      </c>
+      <c r="K8">
+        <v>26.44</v>
+      </c>
+      <c r="L8">
+        <v>28.56</v>
+      </c>
+      <c r="M8">
+        <v>0.9218034000000001</v>
+      </c>
+      <c r="N8">
+        <v>27.6381966</v>
+      </c>
+      <c r="O8">
+        <v>6.909549149999999</v>
+      </c>
+      <c r="P8">
+        <v>20.72864745</v>
+      </c>
+      <c r="Q8">
+        <v>47.16864744999999</v>
+      </c>
+      <c r="R8">
+        <v>0.06382978723404255</v>
+      </c>
+      <c r="S8">
+        <v>0.1061770702535302</v>
+      </c>
+      <c r="T8">
+        <v>1.230260563624244</v>
+      </c>
+      <c r="U8">
+        <v>0.0447</v>
+      </c>
+      <c r="V8">
+        <v>0.25</v>
+      </c>
+      <c r="W8">
+        <v>0.033525</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y8">
+        <v>30.98274534461469</v>
+      </c>
+      <c r="Z8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="B9">
+        <v>0.101604448713348</v>
+      </c>
+      <c r="C9">
+        <v>306.6619570412572</v>
+      </c>
+      <c r="D9">
+        <v>273.5209570412572</v>
+      </c>
+      <c r="E9">
+        <v>-68.041</v>
+      </c>
+      <c r="F9">
+        <v>24.059</v>
+      </c>
+      <c r="G9">
+        <v>57.2</v>
+      </c>
+      <c r="H9">
+        <v>251.6</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>55</v>
+      </c>
+      <c r="K9">
+        <v>26.44</v>
+      </c>
+      <c r="L9">
+        <v>28.56</v>
+      </c>
+      <c r="M9">
+        <v>1.0754373</v>
+      </c>
+      <c r="N9">
+        <v>27.4845627</v>
+      </c>
+      <c r="O9">
+        <v>6.871140674999999</v>
+      </c>
+      <c r="P9">
+        <v>20.613422025</v>
+      </c>
+      <c r="Q9">
+        <v>47.053422025</v>
+      </c>
+      <c r="R9">
+        <v>0.07526881720430109</v>
+      </c>
+      <c r="S9">
+        <v>0.1067287082939226</v>
+      </c>
+      <c r="T9">
+        <v>1.240333107947351</v>
+      </c>
+      <c r="U9">
+        <v>0.0447</v>
+      </c>
+      <c r="V9">
+        <v>0.25</v>
+      </c>
+      <c r="W9">
+        <v>0.033525</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y9">
+        <v>26.55663886681259</v>
+      </c>
+      <c r="Z9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10">
+        <v>0.08</v>
+      </c>
+      <c r="B10">
+        <v>0.1013909513883777</v>
+      </c>
+      <c r="C10">
+        <v>304.1579352330933</v>
+      </c>
+      <c r="D10">
+        <v>274.4539352330933</v>
+      </c>
+      <c r="E10">
+        <v>-64.604</v>
+      </c>
+      <c r="F10">
+        <v>27.496</v>
+      </c>
+      <c r="G10">
+        <v>57.2</v>
+      </c>
+      <c r="H10">
+        <v>251.6</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>55</v>
+      </c>
+      <c r="K10">
+        <v>26.44</v>
+      </c>
+      <c r="L10">
+        <v>28.56</v>
+      </c>
+      <c r="M10">
+        <v>1.2290712</v>
+      </c>
+      <c r="N10">
+        <v>27.3309288</v>
+      </c>
+      <c r="O10">
+        <v>6.8327322</v>
+      </c>
+      <c r="P10">
+        <v>20.4981966</v>
+      </c>
+      <c r="Q10">
+        <v>46.9381966</v>
+      </c>
+      <c r="R10">
+        <v>0.08695652173913043</v>
+      </c>
+      <c r="S10">
+        <v>0.1072923384656279</v>
+      </c>
+      <c r="T10">
+        <v>1.250624620625308</v>
+      </c>
+      <c r="U10">
+        <v>0.0447</v>
+      </c>
+      <c r="V10">
+        <v>0.25</v>
+      </c>
+      <c r="W10">
+        <v>0.033525</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y10">
+        <v>23.23705900846102</v>
+      </c>
+      <c r="Z10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11">
+        <v>0.09</v>
+      </c>
+      <c r="B11">
+        <v>0.1011774540634073</v>
+      </c>
+      <c r="C11">
+        <v>301.6602999744034</v>
+      </c>
+      <c r="D11">
+        <v>275.3932999744034</v>
+      </c>
+      <c r="E11">
+        <v>-61.167</v>
+      </c>
+      <c r="F11">
+        <v>30.933</v>
+      </c>
+      <c r="G11">
+        <v>57.2</v>
+      </c>
+      <c r="H11">
+        <v>251.6</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>55</v>
+      </c>
+      <c r="K11">
+        <v>26.44</v>
+      </c>
+      <c r="L11">
+        <v>28.56</v>
+      </c>
+      <c r="M11">
+        <v>1.3827051</v>
+      </c>
+      <c r="N11">
+        <v>27.1772949</v>
+      </c>
+      <c r="O11">
+        <v>6.794323725</v>
+      </c>
+      <c r="P11">
+        <v>20.382971175</v>
+      </c>
+      <c r="Q11">
+        <v>46.82297117500001</v>
+      </c>
+      <c r="R11">
+        <v>0.0989010989010989</v>
+      </c>
+      <c r="S11">
+        <v>0.1078683561136344</v>
+      </c>
+      <c r="T11">
+        <v>1.261142320395088</v>
+      </c>
+      <c r="U11">
+        <v>0.0447</v>
+      </c>
+      <c r="V11">
+        <v>0.25</v>
+      </c>
+      <c r="W11">
+        <v>0.033525</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y11">
+        <v>20.65516356307647</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12">
+        <v>0.1</v>
+      </c>
+      <c r="B12">
+        <v>0.1009639567384369</v>
+      </c>
+      <c r="C12">
+        <v>299.1691170675252</v>
+      </c>
+      <c r="D12">
+        <v>276.3391170675252</v>
+      </c>
+      <c r="E12">
+        <v>-57.73</v>
+      </c>
+      <c r="F12">
+        <v>34.37</v>
+      </c>
+      <c r="G12">
+        <v>57.2</v>
+      </c>
+      <c r="H12">
+        <v>251.6</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>55</v>
+      </c>
+      <c r="K12">
+        <v>26.44</v>
+      </c>
+      <c r="L12">
+        <v>28.56</v>
+      </c>
+      <c r="M12">
+        <v>1.536339</v>
+      </c>
+      <c r="N12">
+        <v>27.023661</v>
+      </c>
+      <c r="O12">
+        <v>6.755915249999999</v>
+      </c>
+      <c r="P12">
+        <v>20.26774575</v>
+      </c>
+      <c r="Q12">
+        <v>46.70774575</v>
+      </c>
+      <c r="R12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="S12">
+        <v>0.1084571741538188</v>
+      </c>
+      <c r="T12">
+        <v>1.271893746826418</v>
+      </c>
+      <c r="U12">
+        <v>0.0447</v>
+      </c>
+      <c r="V12">
+        <v>0.25</v>
+      </c>
+      <c r="W12">
+        <v>0.033525</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y12">
+        <v>18.58964720676882</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13">
+        <v>0.11</v>
+      </c>
+      <c r="B13">
+        <v>0.1007504594134666</v>
+      </c>
+      <c r="C13">
+        <v>296.6844532218839</v>
+      </c>
+      <c r="D13">
+        <v>277.2914532218839</v>
+      </c>
+      <c r="E13">
+        <v>-54.29299999999999</v>
+      </c>
+      <c r="F13">
+        <v>37.807</v>
+      </c>
+      <c r="G13">
+        <v>57.2</v>
+      </c>
+      <c r="H13">
+        <v>251.6</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>55</v>
+      </c>
+      <c r="K13">
+        <v>26.44</v>
+      </c>
+      <c r="L13">
+        <v>28.56</v>
+      </c>
+      <c r="M13">
+        <v>1.6899729</v>
+      </c>
+      <c r="N13">
+        <v>26.8700271</v>
+      </c>
+      <c r="O13">
+        <v>6.717506774999999</v>
+      </c>
+      <c r="P13">
+        <v>20.152520325</v>
+      </c>
+      <c r="Q13">
+        <v>46.592520325</v>
+      </c>
+      <c r="R13">
+        <v>0.1235955056179775</v>
+      </c>
+      <c r="S13">
+        <v>0.1090592240600748</v>
+      </c>
+      <c r="T13">
+        <v>1.282886778346094</v>
+      </c>
+      <c r="U13">
+        <v>0.0447</v>
+      </c>
+      <c r="V13">
+        <v>0.25</v>
+      </c>
+      <c r="W13">
+        <v>0.033525</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y13">
+        <v>16.89967927888074</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14">
+        <v>0.12</v>
+      </c>
+      <c r="B14">
+        <v>0.1005369620884962</v>
+      </c>
+      <c r="C14">
+        <v>294.2063760696774</v>
+      </c>
+      <c r="D14">
+        <v>278.2503760696774</v>
+      </c>
+      <c r="E14">
+        <v>-50.85599999999999</v>
+      </c>
+      <c r="F14">
+        <v>41.244</v>
+      </c>
+      <c r="G14">
+        <v>57.2</v>
+      </c>
+      <c r="H14">
+        <v>251.6</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>55</v>
+      </c>
+      <c r="K14">
+        <v>26.44</v>
+      </c>
+      <c r="L14">
+        <v>28.56</v>
+      </c>
+      <c r="M14">
+        <v>1.8436068</v>
+      </c>
+      <c r="N14">
+        <v>26.7163932</v>
+      </c>
+      <c r="O14">
+        <v>6.6790983</v>
+      </c>
+      <c r="P14">
+        <v>20.0372949</v>
+      </c>
+      <c r="Q14">
+        <v>46.4772949</v>
+      </c>
+      <c r="R14">
+        <v>0.1363636363636364</v>
+      </c>
+      <c r="S14">
+        <v>0.1096749569187457</v>
+      </c>
+      <c r="T14">
+        <v>1.294129651491216</v>
+      </c>
+      <c r="U14">
+        <v>0.0447</v>
+      </c>
+      <c r="V14">
+        <v>0.25</v>
+      </c>
+      <c r="W14">
+        <v>0.033525</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y14">
+        <v>15.49137267230735</v>
+      </c>
+      <c r="Z14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15">
+        <v>0.13</v>
+      </c>
+      <c r="B15">
+        <v>0.1003234647635259</v>
+      </c>
+      <c r="C15">
+        <v>291.7349541818855</v>
+      </c>
+      <c r="D15">
+        <v>279.2159541818855</v>
+      </c>
+      <c r="E15">
+        <v>-47.419</v>
+      </c>
+      <c r="F15">
+        <v>44.681</v>
+      </c>
+      <c r="G15">
+        <v>57.2</v>
+      </c>
+      <c r="H15">
+        <v>251.6</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>55</v>
+      </c>
+      <c r="K15">
+        <v>26.44</v>
+      </c>
+      <c r="L15">
+        <v>28.56</v>
+      </c>
+      <c r="M15">
+        <v>1.9972407</v>
+      </c>
+      <c r="N15">
+        <v>26.5627593</v>
+      </c>
+      <c r="O15">
+        <v>6.640689825</v>
+      </c>
+      <c r="P15">
+        <v>19.922069475</v>
+      </c>
+      <c r="Q15">
+        <v>46.362069475</v>
+      </c>
+      <c r="R15">
+        <v>0.1494252873563219</v>
+      </c>
+      <c r="S15">
+        <v>0.1103048445557769</v>
+      </c>
+      <c r="T15">
+        <v>1.305630981490249</v>
+      </c>
+      <c r="U15">
+        <v>0.0447</v>
+      </c>
+      <c r="V15">
+        <v>0.25</v>
+      </c>
+      <c r="W15">
+        <v>0.033525</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y15">
+        <v>14.2997286205914</v>
+      </c>
+      <c r="Z15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16">
+        <v>0.14</v>
+      </c>
+      <c r="B16">
+        <v>0.1001099674385556</v>
+      </c>
+      <c r="C16">
+        <v>289.2702570846169</v>
+      </c>
+      <c r="D16">
+        <v>280.1882570846169</v>
+      </c>
+      <c r="E16">
+        <v>-43.98199999999999</v>
+      </c>
+      <c r="F16">
+        <v>48.118</v>
+      </c>
+      <c r="G16">
+        <v>57.2</v>
+      </c>
+      <c r="H16">
+        <v>251.6</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>55</v>
+      </c>
+      <c r="K16">
+        <v>26.44</v>
+      </c>
+      <c r="L16">
+        <v>28.56</v>
+      </c>
+      <c r="M16">
+        <v>2.1508746</v>
+      </c>
+      <c r="N16">
+        <v>26.4091254</v>
+      </c>
+      <c r="O16">
+        <v>6.602281349999999</v>
+      </c>
+      <c r="P16">
+        <v>19.80684405</v>
+      </c>
+      <c r="Q16">
+        <v>46.24684405</v>
+      </c>
+      <c r="R16">
+        <v>0.1627906976744186</v>
+      </c>
+      <c r="S16">
+        <v>0.1109493807425065</v>
+      </c>
+      <c r="T16">
+        <v>1.317399784279958</v>
+      </c>
+      <c r="U16">
+        <v>0.0447</v>
+      </c>
+      <c r="V16">
+        <v>0.25</v>
+      </c>
+      <c r="W16">
+        <v>0.033525</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Aaa/AAA</t>
+        </is>
+      </c>
+      <c r="Y16">
+        <v>13.2783194334063</v>
+      </c>
+      <c r="Z16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17">
+        <v>0.15</v>
+      </c>
+      <c r="B17">
+        <v>0.1000202201135852</v>
+      </c>
+      <c r="C17">
+        <v>286.2440061233298</v>
+      </c>
+      <c r="D17">
+        <v>280.5990061233298</v>
+      </c>
+      <c r="E17">
+        <v>-40.54499999999999</v>
+      </c>
+      <c r="F17">
+        <v>51.555</v>
+      </c>
+      <c r="G17">
+        <v>57.2</v>
+      </c>
+      <c r="H17">
+        <v>251.6</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>55</v>
+      </c>
+      <c r="K17">
+        <v>26.44</v>
+      </c>
+      <c r="L17">
+        <v>28.56</v>
+      </c>
+      <c r="M17">
+        <v>2.361219</v>
+      </c>
+      <c r="N17">
+        <v>26.198781</v>
+      </c>
+      <c r="O17">
+        <v>6.549695249999999</v>
+      </c>
+      <c r="P17">
+        <v>19.64908575</v>
+      </c>
+      <c r="Q17">
+        <v>46.08908575</v>
+      </c>
+      <c r="R17">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S17">
+        <v>0.1116090824865708</v>
+      </c>
+      <c r="T17">
+        <v>1.329445500076483</v>
+      </c>
+      <c r="U17">
+        <v>0.0458</v>
+      </c>
+      <c r="V17">
+        <v>0.25</v>
+      </c>
+      <c r="W17">
+        <v>0.03435</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y17">
+        <v>12.09544730920766</v>
+      </c>
+      <c r="Z17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18">
+        <v>0.16</v>
+      </c>
+      <c r="B18">
+        <v>0.09981497278861486</v>
+      </c>
+      <c r="C18">
+        <v>283.7509087879378</v>
+      </c>
+      <c r="D18">
+        <v>281.5429087879378</v>
+      </c>
+      <c r="E18">
+        <v>-37.108</v>
+      </c>
+      <c r="F18">
+        <v>54.992</v>
+      </c>
+      <c r="G18">
+        <v>57.2</v>
+      </c>
+      <c r="H18">
+        <v>251.6</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>55</v>
+      </c>
+      <c r="K18">
+        <v>26.44</v>
+      </c>
+      <c r="L18">
+        <v>28.56</v>
+      </c>
+      <c r="M18">
+        <v>2.5186336</v>
+      </c>
+      <c r="N18">
+        <v>26.0413664</v>
+      </c>
+      <c r="O18">
+        <v>6.510341599999999</v>
+      </c>
+      <c r="P18">
+        <v>19.5310248</v>
+      </c>
+      <c r="Q18">
+        <v>45.9710248</v>
+      </c>
+      <c r="R18">
+        <v>0.1904761904761905</v>
+      </c>
+      <c r="S18">
+        <v>0.1122844914150177</v>
+      </c>
+      <c r="T18">
+        <v>1.341778018630068</v>
+      </c>
+      <c r="U18">
+        <v>0.0458</v>
+      </c>
+      <c r="V18">
+        <v>0.25</v>
+      </c>
+      <c r="W18">
+        <v>0.03435</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y18">
+        <v>11.33948185238218</v>
+      </c>
+      <c r="Z18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19">
+        <v>0.17</v>
+      </c>
+      <c r="B19">
+        <v>0.09960972546364449</v>
+      </c>
+      <c r="C19">
+        <v>281.2641832457241</v>
+      </c>
+      <c r="D19">
+        <v>282.4931832457241</v>
+      </c>
+      <c r="E19">
+        <v>-33.67099999999999</v>
+      </c>
+      <c r="F19">
+        <v>58.429</v>
+      </c>
+      <c r="G19">
+        <v>57.2</v>
+      </c>
+      <c r="H19">
+        <v>251.6</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>55</v>
+      </c>
+      <c r="K19">
+        <v>26.44</v>
+      </c>
+      <c r="L19">
+        <v>28.56</v>
+      </c>
+      <c r="M19">
+        <v>2.6760482</v>
+      </c>
+      <c r="N19">
+        <v>25.8839518</v>
+      </c>
+      <c r="O19">
+        <v>6.47098795</v>
+      </c>
+      <c r="P19">
+        <v>19.41296385</v>
+      </c>
+      <c r="Q19">
+        <v>45.85296384999999</v>
+      </c>
+      <c r="R19">
+        <v>0.2048192771084338</v>
+      </c>
+      <c r="S19">
+        <v>0.112976175257403</v>
+      </c>
+      <c r="T19">
+        <v>1.354407706305426</v>
+      </c>
+      <c r="U19">
+        <v>0.0458</v>
+      </c>
+      <c r="V19">
+        <v>0.25</v>
+      </c>
+      <c r="W19">
+        <v>0.03435</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y19">
+        <v>10.6724535081244</v>
+      </c>
+      <c r="Z19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20">
+        <v>0.18</v>
+      </c>
+      <c r="B20">
+        <v>0.09940447813867415</v>
+      </c>
+      <c r="C20">
+        <v>278.7838942341575</v>
+      </c>
+      <c r="D20">
+        <v>283.4498942341575</v>
+      </c>
+      <c r="E20">
+        <v>-30.234</v>
+      </c>
+      <c r="F20">
+        <v>61.86599999999999</v>
+      </c>
+      <c r="G20">
+        <v>57.2</v>
+      </c>
+      <c r="H20">
+        <v>251.6</v>
+      </c>
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>55</v>
+      </c>
+      <c r="K20">
+        <v>26.44</v>
+      </c>
+      <c r="L20">
+        <v>28.56</v>
+      </c>
+      <c r="M20">
+        <v>2.8334628</v>
+      </c>
+      <c r="N20">
+        <v>25.7265372</v>
+      </c>
+      <c r="O20">
+        <v>6.4316343</v>
+      </c>
+      <c r="P20">
+        <v>19.2949029</v>
+      </c>
+      <c r="Q20">
+        <v>45.7349029</v>
+      </c>
+      <c r="R20">
+        <v>0.2195121951219512</v>
+      </c>
+      <c r="S20">
+        <v>0.1136847294374075</v>
+      </c>
+      <c r="T20">
+        <v>1.367345435143598</v>
+      </c>
+      <c r="U20">
+        <v>0.0458</v>
+      </c>
+      <c r="V20">
+        <v>0.25</v>
+      </c>
+      <c r="W20">
+        <v>0.03435</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>Aa2/AA</t>
+        </is>
+      </c>
+      <c r="Y20">
+        <v>10.07953942433972</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21">
+        <v>0.19</v>
+      </c>
+      <c r="B21">
+        <v>0.09951273081370382</v>
+      </c>
+      <c r="C21">
+        <v>274.8414943142975</v>
+      </c>
+      <c r="D21">
+        <v>282.9444943142975</v>
+      </c>
+      <c r="E21">
+        <v>-26.797</v>
+      </c>
+      <c r="F21">
+        <v>65.303</v>
+      </c>
+      <c r="G21">
+        <v>57.2</v>
+      </c>
+      <c r="H21">
+        <v>251.6</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>55</v>
+      </c>
+      <c r="K21">
+        <v>26.44</v>
+      </c>
+      <c r="L21">
+        <v>28.56</v>
+      </c>
+      <c r="M21">
+        <v>3.134544</v>
+      </c>
+      <c r="N21">
+        <v>25.425456</v>
+      </c>
+      <c r="O21">
+        <v>6.356363999999999</v>
+      </c>
+      <c r="P21">
+        <v>19.069092</v>
+      </c>
+      <c r="Q21">
+        <v>45.509092</v>
+      </c>
+      <c r="R21">
+        <v>0.2345679012345679</v>
+      </c>
+      <c r="S21">
+        <v>0.1144107787823504</v>
+      </c>
+      <c r="T21">
+        <v>1.38060261407654</v>
+      </c>
+      <c r="U21">
+        <v>0.048</v>
+      </c>
+      <c r="V21">
+        <v>0.25</v>
+      </c>
+      <c r="W21">
+        <v>0.036</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y21">
+        <v>9.111373137528137</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22">
+        <v>0.2</v>
+      </c>
+      <c r="B22">
+        <v>0.09932398348873345</v>
+      </c>
+      <c r="C22">
+        <v>272.2868720650425</v>
+      </c>
+      <c r="D22">
+        <v>283.8268720650426</v>
+      </c>
+      <c r="E22">
+        <v>-23.36</v>
+      </c>
+      <c r="F22">
+        <v>68.73999999999999</v>
+      </c>
+      <c r="G22">
+        <v>57.2</v>
+      </c>
+      <c r="H22">
+        <v>251.6</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>55</v>
+      </c>
+      <c r="K22">
+        <v>26.44</v>
+      </c>
+      <c r="L22">
+        <v>28.56</v>
+      </c>
+      <c r="M22">
+        <v>3.29952</v>
+      </c>
+      <c r="N22">
+        <v>25.26048</v>
+      </c>
+      <c r="O22">
+        <v>6.315119999999999</v>
+      </c>
+      <c r="P22">
+        <v>18.94536</v>
+      </c>
+      <c r="Q22">
+        <v>45.38536</v>
+      </c>
+      <c r="R22">
+        <v>0.25</v>
+      </c>
+      <c r="S22">
+        <v>0.1151549793609168</v>
+      </c>
+      <c r="T22">
+        <v>1.394191222482805</v>
+      </c>
+      <c r="U22">
+        <v>0.048</v>
+      </c>
+      <c r="V22">
+        <v>0.25</v>
+      </c>
+      <c r="W22">
+        <v>0.036</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y22">
+        <v>8.655804480651732</v>
+      </c>
+      <c r="Z22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23">
+        <v>0.21</v>
+      </c>
+      <c r="B23">
+        <v>0.09913523616376309</v>
+      </c>
+      <c r="C23">
+        <v>269.7377705181385</v>
+      </c>
+      <c r="D23">
+        <v>284.7147705181385</v>
+      </c>
+      <c r="E23">
+        <v>-19.923</v>
+      </c>
+      <c r="F23">
+        <v>72.17699999999999</v>
+      </c>
+      <c r="G23">
+        <v>57.2</v>
+      </c>
+      <c r="H23">
+        <v>251.6</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23">
+        <v>55</v>
+      </c>
+      <c r="K23">
+        <v>26.44</v>
+      </c>
+      <c r="L23">
+        <v>28.56</v>
+      </c>
+      <c r="M23">
+        <v>3.464496</v>
+      </c>
+      <c r="N23">
+        <v>25.095504</v>
+      </c>
+      <c r="O23">
+        <v>6.273876</v>
+      </c>
+      <c r="P23">
+        <v>18.821628</v>
+      </c>
+      <c r="Q23">
+        <v>45.261628</v>
+      </c>
+      <c r="R23">
+        <v>0.2658227848101266</v>
+      </c>
+      <c r="S23">
+        <v>0.1159180204604596</v>
+      </c>
+      <c r="T23">
+        <v>1.40812384629176</v>
+      </c>
+      <c r="U23">
+        <v>0.048</v>
+      </c>
+      <c r="V23">
+        <v>0.25</v>
+      </c>
+      <c r="W23">
+        <v>0.036</v>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y23">
+        <v>8.243623314906412</v>
+      </c>
+      <c r="Z23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24">
+        <v>0.22</v>
+      </c>
+      <c r="B24">
+        <v>0.09894648883879273</v>
+      </c>
+      <c r="C24">
+        <v>267.1942416475819</v>
+      </c>
+      <c r="D24">
+        <v>285.6082416475818</v>
+      </c>
+      <c r="E24">
+        <v>-16.48599999999999</v>
+      </c>
+      <c r="F24">
+        <v>75.614</v>
+      </c>
+      <c r="G24">
+        <v>57.2</v>
+      </c>
+      <c r="H24">
+        <v>251.6</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>55</v>
+      </c>
+      <c r="K24">
+        <v>26.44</v>
+      </c>
+      <c r="L24">
+        <v>28.56</v>
+      </c>
+      <c r="M24">
+        <v>3.629472</v>
+      </c>
+      <c r="N24">
+        <v>24.930528</v>
+      </c>
+      <c r="O24">
+        <v>6.232632</v>
+      </c>
+      <c r="P24">
+        <v>18.697896</v>
+      </c>
+      <c r="Q24">
+        <v>45.137896</v>
+      </c>
+      <c r="R24">
+        <v>0.282051282051282</v>
+      </c>
+      <c r="S24">
+        <v>0.1167006267164009</v>
+      </c>
+      <c r="T24">
+        <v>1.422413716865048</v>
+      </c>
+      <c r="U24">
+        <v>0.048</v>
+      </c>
+      <c r="V24">
+        <v>0.25</v>
+      </c>
+      <c r="W24">
+        <v>0.036</v>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>A1/A+</t>
+        </is>
+      </c>
+      <c r="Y24">
+        <v>7.868913164228846</v>
+      </c>
+      <c r="Z24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25">
+        <v>0.23</v>
+      </c>
+      <c r="B25">
+        <v>0.09901649151382239</v>
+      </c>
+      <c r="C25">
+        <v>263.4252173063553</v>
+      </c>
+      <c r="D25">
+        <v>285.2762173063553</v>
+      </c>
+      <c r="E25">
+        <v>-13.04899999999999</v>
+      </c>
+      <c r="F25">
+        <v>79.051</v>
+      </c>
+      <c r="G25">
+        <v>57.2</v>
+      </c>
+      <c r="H25">
+        <v>251.6</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>55</v>
+      </c>
+      <c r="K25">
+        <v>26.44</v>
+      </c>
+      <c r="L25">
+        <v>28.56</v>
+      </c>
+      <c r="M25">
+        <v>3.9130245</v>
+      </c>
+      <c r="N25">
+        <v>24.6469755</v>
+      </c>
+      <c r="O25">
+        <v>6.161743875</v>
+      </c>
+      <c r="P25">
+        <v>18.485231625</v>
+      </c>
+      <c r="Q25">
+        <v>44.925231625</v>
+      </c>
+      <c r="R25">
+        <v>0.2987012987012987</v>
+      </c>
+      <c r="S25">
+        <v>0.1175035604075615</v>
+      </c>
+      <c r="T25">
+        <v>1.437074752907771</v>
+      </c>
+      <c r="U25">
+        <v>0.0495</v>
+      </c>
+      <c r="V25">
+        <v>0.25</v>
+      </c>
+      <c r="W25">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y25">
+        <v>7.298702065371684</v>
+      </c>
+      <c r="Z25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26">
+        <v>0.24</v>
+      </c>
+      <c r="B26">
+        <v>0.09883899418885204</v>
+      </c>
+      <c r="C26">
+        <v>260.8315986143476</v>
+      </c>
+      <c r="D26">
+        <v>286.1195986143476</v>
+      </c>
+      <c r="E26">
+        <v>-9.611999999999995</v>
+      </c>
+      <c r="F26">
+        <v>82.488</v>
+      </c>
+      <c r="G26">
+        <v>57.2</v>
+      </c>
+      <c r="H26">
+        <v>251.6</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>55</v>
+      </c>
+      <c r="K26">
+        <v>26.44</v>
+      </c>
+      <c r="L26">
+        <v>28.56</v>
+      </c>
+      <c r="M26">
+        <v>4.083156</v>
+      </c>
+      <c r="N26">
+        <v>24.476844</v>
+      </c>
+      <c r="O26">
+        <v>6.119211</v>
+      </c>
+      <c r="P26">
+        <v>18.357633</v>
+      </c>
+      <c r="Q26">
+        <v>44.797633</v>
+      </c>
+      <c r="R26">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="S26">
+        <v>0.1183276239327001</v>
+      </c>
+      <c r="T26">
+        <v>1.452121605688462</v>
+      </c>
+      <c r="U26">
+        <v>0.0495</v>
+      </c>
+      <c r="V26">
+        <v>0.25</v>
+      </c>
+      <c r="W26">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y26">
+        <v>6.994589479314531</v>
+      </c>
+      <c r="Z26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27">
+        <v>0.25</v>
+      </c>
+      <c r="B27">
+        <v>0.0986614968638817</v>
+      </c>
+      <c r="C27">
+        <v>258.2429813985455</v>
+      </c>
+      <c r="D27">
+        <v>286.9679813985455</v>
+      </c>
+      <c r="E27">
+        <v>-6.174999999999997</v>
+      </c>
+      <c r="F27">
+        <v>85.925</v>
+      </c>
+      <c r="G27">
+        <v>57.2</v>
+      </c>
+      <c r="H27">
+        <v>251.6</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>55</v>
+      </c>
+      <c r="K27">
+        <v>26.44</v>
+      </c>
+      <c r="L27">
+        <v>28.56</v>
+      </c>
+      <c r="M27">
+        <v>4.2532875</v>
+      </c>
+      <c r="N27">
+        <v>24.3067125</v>
+      </c>
+      <c r="O27">
+        <v>6.076678125</v>
+      </c>
+      <c r="P27">
+        <v>18.230034375</v>
+      </c>
+      <c r="Q27">
+        <v>44.670034375</v>
+      </c>
+      <c r="R27">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="S27">
+        <v>0.1191736624851756</v>
+      </c>
+      <c r="T27">
+        <v>1.467569707876637</v>
+      </c>
+      <c r="U27">
+        <v>0.0495</v>
+      </c>
+      <c r="V27">
+        <v>0.25</v>
+      </c>
+      <c r="W27">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y27">
+        <v>6.714805900141949</v>
+      </c>
+      <c r="Z27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28">
+        <v>0.26</v>
+      </c>
+      <c r="B28">
+        <v>0.09848399953891135</v>
+      </c>
+      <c r="C28">
+        <v>255.6594102813933</v>
+      </c>
+      <c r="D28">
+        <v>287.8214102813934</v>
+      </c>
+      <c r="E28">
+        <v>-2.738</v>
+      </c>
+      <c r="F28">
+        <v>89.36199999999999</v>
+      </c>
+      <c r="G28">
+        <v>57.2</v>
+      </c>
+      <c r="H28">
+        <v>251.6</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>55</v>
+      </c>
+      <c r="K28">
+        <v>26.44</v>
+      </c>
+      <c r="L28">
+        <v>28.56</v>
+      </c>
+      <c r="M28">
+        <v>4.423419</v>
+      </c>
+      <c r="N28">
+        <v>24.136581</v>
+      </c>
+      <c r="O28">
+        <v>6.03414525</v>
+      </c>
+      <c r="P28">
+        <v>18.10243575</v>
+      </c>
+      <c r="Q28">
+        <v>44.54243575</v>
+      </c>
+      <c r="R28">
+        <v>0.3513513513513514</v>
+      </c>
+      <c r="S28">
+        <v>0.1200425669444748</v>
+      </c>
+      <c r="T28">
+        <v>1.483435326340168</v>
+      </c>
+      <c r="U28">
+        <v>0.0495</v>
+      </c>
+      <c r="V28">
+        <v>0.25</v>
+      </c>
+      <c r="W28">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y28">
+        <v>6.456544134751874</v>
+      </c>
+      <c r="Z28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29">
+        <v>0.27</v>
+      </c>
+      <c r="B29">
+        <v>0.09830650221394099</v>
+      </c>
+      <c r="C29">
+        <v>253.0809304177386</v>
+      </c>
+      <c r="D29">
+        <v>288.6799304177387</v>
+      </c>
+      <c r="E29">
+        <v>0.6990000000000123</v>
+      </c>
+      <c r="F29">
+        <v>92.79900000000001</v>
+      </c>
+      <c r="G29">
+        <v>57.2</v>
+      </c>
+      <c r="H29">
+        <v>251.6</v>
+      </c>
+      <c r="I29">
+        <v>0</v>
+      </c>
+      <c r="J29">
+        <v>55</v>
+      </c>
+      <c r="K29">
+        <v>26.44</v>
+      </c>
+      <c r="L29">
+        <v>28.56</v>
+      </c>
+      <c r="M29">
+        <v>4.593550500000001</v>
+      </c>
+      <c r="N29">
+        <v>23.9664495</v>
+      </c>
+      <c r="O29">
+        <v>5.991612374999999</v>
+      </c>
+      <c r="P29">
+        <v>17.974837125</v>
+      </c>
+      <c r="Q29">
+        <v>44.414837125</v>
+      </c>
+      <c r="R29">
+        <v>0.3698630136986302</v>
+      </c>
+      <c r="S29">
+        <v>0.1209352770053986</v>
+      </c>
+      <c r="T29">
+        <v>1.499735619282152</v>
+      </c>
+      <c r="U29">
+        <v>0.0495</v>
+      </c>
+      <c r="V29">
+        <v>0.25</v>
+      </c>
+      <c r="W29">
+        <v>0.03712500000000001</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>A2/A</t>
+        </is>
+      </c>
+      <c r="Y29">
+        <v>6.217412870501803</v>
+      </c>
+      <c r="Z29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0.28</v>
+      </c>
+      <c r="B30">
+        <v>0.09842300488897064</v>
+      </c>
+      <c r="C30">
+        <v>249.0798531092623</v>
+      </c>
+      <c r="D30">
+        <v>288.1158531092623</v>
+      </c>
+      <c r="E30">
+        <v>4.13600000000001</v>
+      </c>
+      <c r="F30">
+        <v>96.236</v>
+      </c>
+      <c r="G30">
+        <v>57.2</v>
+      </c>
+      <c r="H30">
+        <v>251.6</v>
+      </c>
+      <c r="I30">
+        <v>0</v>
+      </c>
+      <c r="J30">
+        <v>55</v>
+      </c>
+      <c r="K30">
+        <v>26.44</v>
+      </c>
+      <c r="L30">
+        <v>28.56</v>
+      </c>
+      <c r="M30">
+        <v>4.898412400000001</v>
+      </c>
+      <c r="N30">
+        <v>23.6615876</v>
+      </c>
+      <c r="O30">
+        <v>5.915396899999999</v>
+      </c>
+      <c r="P30">
+        <v>17.7461907</v>
+      </c>
+      <c r="Q30">
+        <v>44.1861907</v>
+      </c>
+      <c r="R30">
+        <v>0.388888888888889</v>
+      </c>
+      <c r="S30">
+        <v>0.1218527845680148</v>
+      </c>
+      <c r="T30">
+        <v>1.516488698139191</v>
+      </c>
+      <c r="U30">
+        <v>0.0509</v>
+      </c>
+      <c r="V30">
+        <v>0.25</v>
+      </c>
+      <c r="W30">
+        <v>0.038175</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y30">
+        <v>5.830460497772705</v>
+      </c>
+      <c r="Z30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.29</v>
+      </c>
+      <c r="B31">
+        <v>0.09825600756400028</v>
+      </c>
+      <c r="C31">
+        <v>246.4520997896589</v>
+      </c>
+      <c r="D31">
+        <v>288.9250997896589</v>
+      </c>
+      <c r="E31">
+        <v>7.572999999999993</v>
+      </c>
+      <c r="F31">
+        <v>99.67299999999999</v>
+      </c>
+      <c r="G31">
+        <v>57.2</v>
+      </c>
+      <c r="H31">
+        <v>251.6</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>55</v>
+      </c>
+      <c r="K31">
+        <v>26.44</v>
+      </c>
+      <c r="L31">
+        <v>28.56</v>
+      </c>
+      <c r="M31">
+        <v>5.0733557</v>
+      </c>
+      <c r="N31">
+        <v>23.4866443</v>
+      </c>
+      <c r="O31">
+        <v>5.871661075</v>
+      </c>
+      <c r="P31">
+        <v>17.614983225</v>
+      </c>
+      <c r="Q31">
+        <v>44.054983225</v>
+      </c>
+      <c r="R31">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="S31">
+        <v>0.1227961374140849</v>
+      </c>
+      <c r="T31">
+        <v>1.533713694710513</v>
+      </c>
+      <c r="U31">
+        <v>0.0509</v>
+      </c>
+      <c r="V31">
+        <v>0.25</v>
+      </c>
+      <c r="W31">
+        <v>0.038175</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y31">
+        <v>5.629410135780545</v>
+      </c>
+      <c r="Z31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.3</v>
+      </c>
+      <c r="B32">
+        <v>0.09808901023902993</v>
+      </c>
+      <c r="C32">
+        <v>243.8289052248844</v>
+      </c>
+      <c r="D32">
+        <v>289.7389052248844</v>
+      </c>
+      <c r="E32">
+        <v>11.01000000000001</v>
+      </c>
+      <c r="F32">
+        <v>103.11</v>
+      </c>
+      <c r="G32">
+        <v>57.2</v>
+      </c>
+      <c r="H32">
+        <v>251.6</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>55</v>
+      </c>
+      <c r="K32">
+        <v>26.44</v>
+      </c>
+      <c r="L32">
+        <v>28.56</v>
+      </c>
+      <c r="M32">
+        <v>5.248299</v>
+      </c>
+      <c r="N32">
+        <v>23.311701</v>
+      </c>
+      <c r="O32">
+        <v>5.82792525</v>
+      </c>
+      <c r="P32">
+        <v>17.48377575</v>
+      </c>
+      <c r="Q32">
+        <v>43.92377575</v>
+      </c>
+      <c r="R32">
+        <v>0.4285714285714286</v>
+      </c>
+      <c r="S32">
+        <v>0.1237664431986142</v>
+      </c>
+      <c r="T32">
+        <v>1.551430834041016</v>
+      </c>
+      <c r="U32">
+        <v>0.0509</v>
+      </c>
+      <c r="V32">
+        <v>0.25</v>
+      </c>
+      <c r="W32">
+        <v>0.038175</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y32">
+        <v>5.441763131254526</v>
+      </c>
+      <c r="Z32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.31</v>
+      </c>
+      <c r="B33">
+        <v>0.09792201291405958</v>
+      </c>
+      <c r="C33">
+        <v>241.2103080452135</v>
+      </c>
+      <c r="D33">
+        <v>290.5573080452135</v>
+      </c>
+      <c r="E33">
+        <v>14.447</v>
+      </c>
+      <c r="F33">
+        <v>106.547</v>
+      </c>
+      <c r="G33">
+        <v>57.2</v>
+      </c>
+      <c r="H33">
+        <v>251.6</v>
+      </c>
+      <c r="I33">
+        <v>0</v>
+      </c>
+      <c r="J33">
+        <v>55</v>
+      </c>
+      <c r="K33">
+        <v>26.44</v>
+      </c>
+      <c r="L33">
+        <v>28.56</v>
+      </c>
+      <c r="M33">
+        <v>5.4232423</v>
+      </c>
+      <c r="N33">
+        <v>23.1367577</v>
+      </c>
+      <c r="O33">
+        <v>5.784189424999999</v>
+      </c>
+      <c r="P33">
+        <v>17.352568275</v>
+      </c>
+      <c r="Q33">
+        <v>43.79256827499999</v>
+      </c>
+      <c r="R33">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="S33">
+        <v>0.1247648737884921</v>
+      </c>
+      <c r="T33">
+        <v>1.569661513641968</v>
+      </c>
+      <c r="U33">
+        <v>0.0509</v>
+      </c>
+      <c r="V33">
+        <v>0.25</v>
+      </c>
+      <c r="W33">
+        <v>0.038175</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y33">
+        <v>5.266222385085025</v>
+      </c>
+      <c r="Z33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>0.32</v>
+      </c>
+      <c r="B34">
+        <v>0.09775501558908925</v>
+      </c>
+      <c r="C34">
+        <v>238.5963473186202</v>
+      </c>
+      <c r="D34">
+        <v>291.3803473186202</v>
+      </c>
+      <c r="E34">
+        <v>17.884</v>
+      </c>
+      <c r="F34">
+        <v>109.984</v>
+      </c>
+      <c r="G34">
+        <v>57.2</v>
+      </c>
+      <c r="H34">
+        <v>251.6</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>55</v>
+      </c>
+      <c r="K34">
+        <v>26.44</v>
+      </c>
+      <c r="L34">
+        <v>28.56</v>
+      </c>
+      <c r="M34">
+        <v>5.5981856</v>
+      </c>
+      <c r="N34">
+        <v>22.9618144</v>
+      </c>
+      <c r="O34">
+        <v>5.740453599999999</v>
+      </c>
+      <c r="P34">
+        <v>17.2213608</v>
+      </c>
+      <c r="Q34">
+        <v>43.6613608</v>
+      </c>
+      <c r="R34">
+        <v>0.4705882352941177</v>
+      </c>
+      <c r="S34">
+        <v>0.1257926699839548</v>
+      </c>
+      <c r="T34">
+        <v>1.588428389701772</v>
+      </c>
+      <c r="U34">
+        <v>0.0509</v>
+      </c>
+      <c r="V34">
+        <v>0.25</v>
+      </c>
+      <c r="W34">
+        <v>0.038175</v>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y34">
+        <v>5.101652935551118</v>
+      </c>
+      <c r="Z34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>0.33</v>
+      </c>
+      <c r="B35">
+        <v>0.09758801826411888</v>
+      </c>
+      <c r="C35">
+        <v>235.9870625569964</v>
+      </c>
+      <c r="D35">
+        <v>292.2080625569964</v>
+      </c>
+      <c r="E35">
+        <v>21.32100000000001</v>
+      </c>
+      <c r="F35">
+        <v>113.421</v>
+      </c>
+      <c r="G35">
+        <v>57.2</v>
+      </c>
+      <c r="H35">
+        <v>251.6</v>
+      </c>
+      <c r="I35">
+        <v>0</v>
+      </c>
+      <c r="J35">
+        <v>55</v>
+      </c>
+      <c r="K35">
+        <v>26.44</v>
+      </c>
+      <c r="L35">
+        <v>28.56</v>
+      </c>
+      <c r="M35">
+        <v>5.773128900000001</v>
+      </c>
+      <c r="N35">
+        <v>22.7868711</v>
+      </c>
+      <c r="O35">
+        <v>5.696717775</v>
+      </c>
+      <c r="P35">
+        <v>17.090153325</v>
+      </c>
+      <c r="Q35">
+        <v>43.530153325</v>
+      </c>
+      <c r="R35">
+        <v>0.4925373134328359</v>
+      </c>
+      <c r="S35">
+        <v>0.126851146662864</v>
+      </c>
+      <c r="T35">
+        <v>1.607755471017092</v>
+      </c>
+      <c r="U35">
+        <v>0.0509</v>
+      </c>
+      <c r="V35">
+        <v>0.25</v>
+      </c>
+      <c r="W35">
+        <v>0.038175</v>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y35">
+        <v>4.947057392049569</v>
+      </c>
+      <c r="Z35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>0.34</v>
+      </c>
+      <c r="B36">
+        <v>0.09742102093914853</v>
+      </c>
+      <c r="C36">
+        <v>233.3824937224727</v>
+      </c>
+      <c r="D36">
+        <v>293.0404937224727</v>
+      </c>
+      <c r="E36">
+        <v>24.75800000000001</v>
+      </c>
+      <c r="F36">
+        <v>116.858</v>
+      </c>
+      <c r="G36">
+        <v>57.2</v>
+      </c>
+      <c r="H36">
+        <v>251.6</v>
+      </c>
+      <c r="I36">
+        <v>0</v>
+      </c>
+      <c r="J36">
+        <v>55</v>
+      </c>
+      <c r="K36">
+        <v>26.44</v>
+      </c>
+      <c r="L36">
+        <v>28.56</v>
+      </c>
+      <c r="M36">
+        <v>5.9480722</v>
+      </c>
+      <c r="N36">
+        <v>22.6119278</v>
+      </c>
+      <c r="O36">
+        <v>5.652981949999999</v>
+      </c>
+      <c r="P36">
+        <v>16.95894585</v>
+      </c>
+      <c r="Q36">
+        <v>43.39894585</v>
+      </c>
+      <c r="R36">
+        <v>0.5151515151515152</v>
+      </c>
+      <c r="S36">
+        <v>0.1279416983926493</v>
+      </c>
+      <c r="T36">
+        <v>1.627668221463179</v>
+      </c>
+      <c r="U36">
+        <v>0.0509</v>
+      </c>
+      <c r="V36">
+        <v>0.25</v>
+      </c>
+      <c r="W36">
+        <v>0.038175</v>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y36">
+        <v>4.801555704048111</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>0.35</v>
+      </c>
+      <c r="B37">
+        <v>0.09725402361417819</v>
+      </c>
+      <c r="C37">
+        <v>230.7826812338516</v>
+      </c>
+      <c r="D37">
+        <v>293.8776812338517</v>
+      </c>
+      <c r="E37">
+        <v>28.19500000000001</v>
+      </c>
+      <c r="F37">
+        <v>120.295</v>
+      </c>
+      <c r="G37">
+        <v>57.2</v>
+      </c>
+      <c r="H37">
+        <v>251.6</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>55</v>
+      </c>
+      <c r="K37">
+        <v>26.44</v>
+      </c>
+      <c r="L37">
+        <v>28.56</v>
+      </c>
+      <c r="M37">
+        <v>6.1230155</v>
+      </c>
+      <c r="N37">
+        <v>22.4369845</v>
+      </c>
+      <c r="O37">
+        <v>5.609246124999999</v>
+      </c>
+      <c r="P37">
+        <v>16.827738375</v>
+      </c>
+      <c r="Q37">
+        <v>43.267738375</v>
+      </c>
+      <c r="R37">
+        <v>0.5384615384615385</v>
+      </c>
+      <c r="S37">
+        <v>0.1290658055602741</v>
+      </c>
+      <c r="T37">
+        <v>1.648193671922992</v>
+      </c>
+      <c r="U37">
+        <v>0.0509</v>
+      </c>
+      <c r="V37">
+        <v>0.25</v>
+      </c>
+      <c r="W37">
+        <v>0.038175</v>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y37">
+        <v>4.664368398218166</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>0.36</v>
+      </c>
+      <c r="B38">
+        <v>0.09708702628920783</v>
+      </c>
+      <c r="C38">
+        <v>228.1876659731492</v>
+      </c>
+      <c r="D38">
+        <v>294.7196659731492</v>
+      </c>
+      <c r="E38">
+        <v>31.63199999999999</v>
+      </c>
+      <c r="F38">
+        <v>123.732</v>
+      </c>
+      <c r="G38">
+        <v>57.2</v>
+      </c>
+      <c r="H38">
+        <v>251.6</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>55</v>
+      </c>
+      <c r="K38">
+        <v>26.44</v>
+      </c>
+      <c r="L38">
+        <v>28.56</v>
+      </c>
+      <c r="M38">
+        <v>6.297958799999999</v>
+      </c>
+      <c r="N38">
+        <v>22.2620412</v>
+      </c>
+      <c r="O38">
+        <v>5.5655103</v>
+      </c>
+      <c r="P38">
+        <v>16.6965309</v>
+      </c>
+      <c r="Q38">
+        <v>43.1365309</v>
+      </c>
+      <c r="R38">
+        <v>0.5625</v>
+      </c>
+      <c r="S38">
+        <v>0.1302250410768872</v>
+      </c>
+      <c r="T38">
+        <v>1.669360542709674</v>
+      </c>
+      <c r="U38">
+        <v>0.0509</v>
+      </c>
+      <c r="V38">
+        <v>0.25</v>
+      </c>
+      <c r="W38">
+        <v>0.038175</v>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>A3/A-</t>
+        </is>
+      </c>
+      <c r="Y38">
+        <v>4.534802609378772</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>0.37</v>
+      </c>
+      <c r="B39">
+        <v>0.09764152896423747</v>
+      </c>
+      <c r="C39">
+        <v>221.9733274837758</v>
+      </c>
+      <c r="D39">
+        <v>291.9423274837758</v>
+      </c>
+      <c r="E39">
+        <v>35.069</v>
+      </c>
+      <c r="F39">
+        <v>127.169</v>
+      </c>
+      <c r="G39">
+        <v>57.2</v>
+      </c>
+      <c r="H39">
+        <v>251.6</v>
+      </c>
+      <c r="I39">
+        <v>0</v>
+      </c>
+      <c r="J39">
+        <v>55</v>
+      </c>
+      <c r="K39">
+        <v>26.44</v>
+      </c>
+      <c r="L39">
+        <v>28.56</v>
+      </c>
+      <c r="M39">
+        <v>6.8035415</v>
+      </c>
+      <c r="N39">
+        <v>21.7564585</v>
+      </c>
+      <c r="O39">
+        <v>5.439114625</v>
+      </c>
+      <c r="P39">
+        <v>16.317343875</v>
+      </c>
+      <c r="Q39">
+        <v>42.757343875</v>
+      </c>
+      <c r="R39">
+        <v>0.5873015873015873</v>
+      </c>
+      <c r="S39">
+        <v>0.1314210777210119</v>
+      </c>
+      <c r="T39">
+        <v>1.691199377648315</v>
+      </c>
+      <c r="U39">
+        <v>0.0535</v>
+      </c>
+      <c r="V39">
+        <v>0.25</v>
+      </c>
+      <c r="W39">
+        <v>0.040125</v>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y39">
+        <v>4.197813741563861</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>0.38</v>
+      </c>
+      <c r="B40">
+        <v>0.09749403163926712</v>
+      </c>
+      <c r="C40">
+        <v>219.2699746902606</v>
+      </c>
+      <c r="D40">
+        <v>292.6759746902606</v>
+      </c>
+      <c r="E40">
+        <v>38.506</v>
+      </c>
+      <c r="F40">
+        <v>130.606</v>
+      </c>
+      <c r="G40">
+        <v>57.2</v>
+      </c>
+      <c r="H40">
+        <v>251.6</v>
+      </c>
+      <c r="I40">
+        <v>0</v>
+      </c>
+      <c r="J40">
+        <v>55</v>
+      </c>
+      <c r="K40">
+        <v>26.44</v>
+      </c>
+      <c r="L40">
+        <v>28.56</v>
+      </c>
+      <c r="M40">
+        <v>6.987420999999999</v>
+      </c>
+      <c r="N40">
+        <v>21.572579</v>
+      </c>
+      <c r="O40">
+        <v>5.393144749999999</v>
+      </c>
+      <c r="P40">
+        <v>16.17943425</v>
+      </c>
+      <c r="Q40">
+        <v>42.61943425</v>
+      </c>
+      <c r="R40">
+        <v>0.6129032258064516</v>
+      </c>
+      <c r="S40">
+        <v>0.1326556961923663</v>
+      </c>
+      <c r="T40">
+        <v>1.713742691133363</v>
+      </c>
+      <c r="U40">
+        <v>0.0535</v>
+      </c>
+      <c r="V40">
+        <v>0.25</v>
+      </c>
+      <c r="W40">
+        <v>0.040125</v>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>Baa2/BBB</t>
+        </is>
+      </c>
+      <c r="Y40">
+        <v>4.087344958891127</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>0.39</v>
+      </c>
+      <c r="B41">
+        <v>0.09813628431429677</v>
+      </c>
+      <c r="C41">
+        <v>212.6650660516598</v>
+      </c>
+      <c r="D41">
+        <v>289.5080660516599</v>
+      </c>
+      <c r="E41">
+        <v>41.94300000000001</v>
+      </c>
+      <c r="F41">
+        <v>134.043</v>
+      </c>
+      <c r="G41">
+        <v>57.2</v>
+      </c>
+      <c r="H41">
+        <v>251.6</v>
+      </c>
+      <c r="I41">
+        <v>0</v>
+      </c>
+      <c r="J41">
+        <v>55</v>
+      </c>
+      <c r="K41">
+        <v>26.44</v>
+      </c>
+      <c r="L41">
+        <v>28.56</v>
+      </c>
+      <c r="M41">
+        <v>7.5332166</v>
+      </c>
+      <c r="N41">
+        <v>21.0267834</v>
+      </c>
+      <c r="O41">
+        <v>5.25669585</v>
+      </c>
+      <c r="P41">
+        <v>15.77008755</v>
+      </c>
+      <c r="Q41">
+        <v>42.21008755</v>
+      </c>
+      <c r="R41">
+        <v>0.639344262295082</v>
+      </c>
+      <c r="S41">
+        <v>0.1339307939578636</v>
+      </c>
+      <c r="T41">
+        <v>1.737025129650708</v>
+      </c>
+      <c r="U41">
+        <v>0.0562</v>
+      </c>
+      <c r="V41">
+        <v>0.25</v>
+      </c>
+      <c r="W41">
+        <v>0.04215</v>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y41">
+        <v>3.791209189445051</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>0.4</v>
+      </c>
+      <c r="B42">
+        <v>0.09800903698932642</v>
+      </c>
+      <c r="C42">
+        <v>209.8502536236187</v>
+      </c>
+      <c r="D42">
+        <v>290.1302536236187</v>
+      </c>
+      <c r="E42">
+        <v>45.38</v>
+      </c>
+      <c r="F42">
+        <v>137.48</v>
+      </c>
+      <c r="G42">
+        <v>57.2</v>
+      </c>
+      <c r="H42">
+        <v>251.6</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>55</v>
+      </c>
+      <c r="K42">
+        <v>26.44</v>
+      </c>
+      <c r="L42">
+        <v>28.56</v>
+      </c>
+      <c r="M42">
+        <v>7.726375999999999</v>
+      </c>
+      <c r="N42">
+        <v>20.833624</v>
+      </c>
+      <c r="O42">
+        <v>5.208406</v>
+      </c>
+      <c r="P42">
+        <v>15.625218</v>
+      </c>
+      <c r="Q42">
+        <v>42.065218</v>
+      </c>
+      <c r="R42">
+        <v>0.6666666666666667</v>
+      </c>
+      <c r="S42">
+        <v>0.1352483949822107</v>
+      </c>
+      <c r="T42">
+        <v>1.761083649451964</v>
+      </c>
+      <c r="U42">
+        <v>0.0562</v>
+      </c>
+      <c r="V42">
+        <v>0.25</v>
+      </c>
+      <c r="W42">
+        <v>0.04215</v>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y42">
+        <v>3.696428959708925</v>
+      </c>
+      <c r="Z42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>0.41</v>
+      </c>
+      <c r="B43">
+        <v>0.09788178966435607</v>
+      </c>
+      <c r="C43">
+        <v>207.038121266869</v>
+      </c>
+      <c r="D43">
+        <v>290.755121266869</v>
+      </c>
+      <c r="E43">
+        <v>48.81700000000001</v>
+      </c>
+      <c r="F43">
+        <v>140.917</v>
+      </c>
+      <c r="G43">
+        <v>57.2</v>
+      </c>
+      <c r="H43">
+        <v>251.6</v>
+      </c>
+      <c r="I43">
+        <v>0</v>
+      </c>
+      <c r="J43">
+        <v>55</v>
+      </c>
+      <c r="K43">
+        <v>26.44</v>
+      </c>
+      <c r="L43">
+        <v>28.56</v>
+      </c>
+      <c r="M43">
+        <v>7.9195354</v>
+      </c>
+      <c r="N43">
+        <v>20.6404646</v>
+      </c>
+      <c r="O43">
+        <v>5.160116149999999</v>
+      </c>
+      <c r="P43">
+        <v>15.48034845</v>
+      </c>
+      <c r="Q43">
+        <v>41.92034845</v>
+      </c>
+      <c r="R43">
+        <v>0.6949152542372882</v>
+      </c>
+      <c r="S43">
+        <v>0.1366106604480611</v>
+      </c>
+      <c r="T43">
+        <v>1.785957712297331</v>
+      </c>
+      <c r="U43">
+        <v>0.0562</v>
+      </c>
+      <c r="V43">
+        <v>0.25</v>
+      </c>
+      <c r="W43">
+        <v>0.04215</v>
+      </c>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y43">
+        <v>3.606272155813584</v>
+      </c>
+      <c r="Z43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>0.42</v>
+      </c>
+      <c r="B44">
+        <v>0.09775454233938573</v>
+      </c>
+      <c r="C44">
+        <v>204.2286863353866</v>
+      </c>
+      <c r="D44">
+        <v>291.3826863353866</v>
+      </c>
+      <c r="E44">
+        <v>52.25399999999999</v>
+      </c>
+      <c r="F44">
+        <v>144.354</v>
+      </c>
+      <c r="G44">
+        <v>57.2</v>
+      </c>
+      <c r="H44">
+        <v>251.6</v>
+      </c>
+      <c r="I44">
+        <v>0</v>
+      </c>
+      <c r="J44">
+        <v>55</v>
+      </c>
+      <c r="K44">
+        <v>26.44</v>
+      </c>
+      <c r="L44">
+        <v>28.56</v>
+      </c>
+      <c r="M44">
+        <v>8.1126948</v>
+      </c>
+      <c r="N44">
+        <v>20.4473052</v>
+      </c>
+      <c r="O44">
+        <v>5.1118263</v>
+      </c>
+      <c r="P44">
+        <v>15.3354789</v>
+      </c>
+      <c r="Q44">
+        <v>41.7754789</v>
+      </c>
+      <c r="R44">
+        <v>0.7241379310344827</v>
+      </c>
+      <c r="S44">
+        <v>0.1380199005851478</v>
+      </c>
+      <c r="T44">
+        <v>1.81168950144771</v>
+      </c>
+      <c r="U44">
+        <v>0.0562</v>
+      </c>
+      <c r="V44">
+        <v>0.25</v>
+      </c>
+      <c r="W44">
+        <v>0.04215</v>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>Ba1/BB+</t>
+        </is>
+      </c>
+      <c r="Y44">
+        <v>3.520408533056118</v>
+      </c>
+      <c r="Z44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>0.43</v>
+      </c>
+      <c r="B45">
+        <v>0.09914304501441538</v>
+      </c>
+      <c r="C45">
+        <v>194.0869262534689</v>
+      </c>
+      <c r="D45">
+        <v>284.6779262534689</v>
+      </c>
+      <c r="E45">
+        <v>55.691</v>
+      </c>
+      <c r="F45">
+        <v>147.791</v>
+      </c>
+      <c r="G45">
+        <v>57.2</v>
+      </c>
+      <c r="H45">
+        <v>251.6</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>55</v>
+      </c>
+      <c r="K45">
+        <v>26.44</v>
+      </c>
+      <c r="L45">
+        <v>28.56</v>
+      </c>
+      <c r="M45">
+        <v>9.000471900000001</v>
+      </c>
+      <c r="N45">
+        <v>19.5595281</v>
+      </c>
+      <c r="O45">
+        <v>4.889882024999999</v>
+      </c>
+      <c r="P45">
+        <v>14.669646075</v>
+      </c>
+      <c r="Q45">
+        <v>41.109646075</v>
+      </c>
+      <c r="R45">
+        <v>0.7543859649122806</v>
+      </c>
+      <c r="S45">
+        <v>0.1394785877445884</v>
+      </c>
+      <c r="T45">
+        <v>1.83832416039284</v>
+      </c>
+      <c r="U45">
+        <v>0.0609</v>
+      </c>
+      <c r="V45">
+        <v>0.25</v>
+      </c>
+      <c r="W45">
+        <v>0.045675</v>
+      </c>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y45">
+        <v>3.173166953612732</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>0.44</v>
+      </c>
+      <c r="B46">
+        <v>0.09905104768944505</v>
+      </c>
+      <c r="C46">
+        <v>191.0846009802622</v>
+      </c>
+      <c r="D46">
+        <v>285.1126009802622</v>
+      </c>
+      <c r="E46">
+        <v>59.12800000000001</v>
+      </c>
+      <c r="F46">
+        <v>151.228</v>
+      </c>
+      <c r="G46">
+        <v>57.2</v>
+      </c>
+      <c r="H46">
+        <v>251.6</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>55</v>
+      </c>
+      <c r="K46">
+        <v>26.44</v>
+      </c>
+      <c r="L46">
+        <v>28.56</v>
+      </c>
+      <c r="M46">
+        <v>9.209785200000001</v>
+      </c>
+      <c r="N46">
+        <v>19.3502148</v>
+      </c>
+      <c r="O46">
+        <v>4.837553699999999</v>
+      </c>
+      <c r="P46">
+        <v>14.5126611</v>
+      </c>
+      <c r="Q46">
+        <v>40.9526611</v>
+      </c>
+      <c r="R46">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="S46">
+        <v>0.140989370874009</v>
+      </c>
+      <c r="T46">
+        <v>1.865910057157438</v>
+      </c>
+      <c r="U46">
+        <v>0.0609</v>
+      </c>
+      <c r="V46">
+        <v>0.25</v>
+      </c>
+      <c r="W46">
+        <v>0.045675</v>
+      </c>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y46">
+        <v>3.101049522848806</v>
+      </c>
+      <c r="Z46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>0.45</v>
+      </c>
+      <c r="B47">
+        <v>0.09895905036447465</v>
+      </c>
+      <c r="C47">
+        <v>188.0836051466615</v>
+      </c>
+      <c r="D47">
+        <v>285.5486051466615</v>
+      </c>
+      <c r="E47">
+        <v>62.565</v>
+      </c>
+      <c r="F47">
+        <v>154.665</v>
+      </c>
+      <c r="G47">
+        <v>57.2</v>
+      </c>
+      <c r="H47">
+        <v>251.6</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>55</v>
+      </c>
+      <c r="K47">
+        <v>26.44</v>
+      </c>
+      <c r="L47">
+        <v>28.56</v>
+      </c>
+      <c r="M47">
+        <v>9.4190985</v>
+      </c>
+      <c r="N47">
+        <v>19.1409015</v>
+      </c>
+      <c r="O47">
+        <v>4.785225375</v>
+      </c>
+      <c r="P47">
+        <v>14.355676125</v>
+      </c>
+      <c r="Q47">
+        <v>40.795676125</v>
+      </c>
+      <c r="R47">
+        <v>0.8181818181818181</v>
+      </c>
+      <c r="S47">
+        <v>0.1425550915717721</v>
+      </c>
+      <c r="T47">
+        <v>1.894499077440749</v>
+      </c>
+      <c r="U47">
+        <v>0.0609</v>
+      </c>
+      <c r="V47">
+        <v>0.25</v>
+      </c>
+      <c r="W47">
+        <v>0.045675</v>
+      </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>Ba2/BB</t>
+        </is>
+      </c>
+      <c r="Y47">
+        <v>3.032137311229944</v>
+      </c>
+      <c r="Z47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>0.46</v>
+      </c>
+      <c r="B48">
+        <v>0.1020755530395043</v>
+      </c>
+      <c r="C48">
+        <v>170.5825164260941</v>
+      </c>
+      <c r="D48">
+        <v>271.4845164260941</v>
+      </c>
+      <c r="E48">
+        <v>66.00200000000001</v>
+      </c>
+      <c r="F48">
+        <v>158.102</v>
+      </c>
+      <c r="G48">
+        <v>57.2</v>
+      </c>
+      <c r="H48">
+        <v>251.6</v>
+      </c>
+      <c r="I48">
+        <v>0</v>
+      </c>
+      <c r="J48">
+        <v>55</v>
+      </c>
+      <c r="K48">
+        <v>26.44</v>
+      </c>
+      <c r="L48">
+        <v>28.56</v>
+      </c>
+      <c r="M48">
+        <v>11.0987604</v>
+      </c>
+      <c r="N48">
+        <v>17.4612396</v>
+      </c>
+      <c r="O48">
+        <v>4.3653099</v>
+      </c>
+      <c r="P48">
+        <v>13.0959297</v>
+      </c>
+      <c r="Q48">
+        <v>39.5359297</v>
+      </c>
+      <c r="R48">
+        <v>0.8518518518518519</v>
+      </c>
+      <c r="S48">
+        <v>0.144178801925008</v>
+      </c>
+      <c r="T48">
+        <v>1.924146950327146</v>
+      </c>
+      <c r="U48">
+        <v>0.0702</v>
+      </c>
+      <c r="V48">
+        <v>0.25</v>
+      </c>
+      <c r="W48">
+        <v>0.05265</v>
+      </c>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y48">
+        <v>2.57326034356053</v>
+      </c>
+      <c r="Z48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>0.47</v>
+      </c>
+      <c r="B49">
+        <v>0.102053305714534</v>
+      </c>
+      <c r="C49">
+        <v>167.2410024120535</v>
+      </c>
+      <c r="D49">
+        <v>271.5800024120535</v>
+      </c>
+      <c r="E49">
+        <v>69.43900000000002</v>
+      </c>
+      <c r="F49">
+        <v>161.539</v>
+      </c>
+      <c r="G49">
+        <v>57.2</v>
+      </c>
+      <c r="H49">
+        <v>251.6</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>55</v>
+      </c>
+      <c r="K49">
+        <v>26.44</v>
+      </c>
+      <c r="L49">
+        <v>28.56</v>
+      </c>
+      <c r="M49">
+        <v>11.3400378</v>
+      </c>
+      <c r="N49">
+        <v>17.2199622</v>
+      </c>
+      <c r="O49">
+        <v>4.304990549999999</v>
+      </c>
+      <c r="P49">
+        <v>12.91497165</v>
+      </c>
+      <c r="Q49">
+        <v>39.35497165</v>
+      </c>
+      <c r="R49">
+        <v>0.8867924528301887</v>
+      </c>
+      <c r="S49">
+        <v>0.1458637843670452</v>
+      </c>
+      <c r="T49">
+        <v>1.954913610869633</v>
+      </c>
+      <c r="U49">
+        <v>0.0702</v>
+      </c>
+      <c r="V49">
+        <v>0.25</v>
+      </c>
+      <c r="W49">
+        <v>0.05265</v>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>B1/B+</t>
+        </is>
+      </c>
+      <c r="Y49">
+        <v>2.518510123484774</v>
+      </c>
+      <c r="Z49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>0.48</v>
+      </c>
+      <c r="B50">
+        <v>0.1037230583895636</v>
+      </c>
+      <c r="C50">
+        <v>156.8192508190051</v>
+      </c>
+      <c r="D50">
+        <v>264.5952508190051</v>
+      </c>
+      <c r="E50">
+        <v>72.876</v>
+      </c>
+      <c r="F50">
+        <v>164.976</v>
+      </c>
+      <c r="G50">
+        <v>57.2</v>
+      </c>
+      <c r="H50">
+        <v>251.6</v>
+      </c>
+      <c r="I50">
+        <v>0</v>
+      </c>
+      <c r="J50">
+        <v>55</v>
+      </c>
+      <c r="K50">
+        <v>26.44</v>
+      </c>
+      <c r="L50">
+        <v>28.56</v>
+      </c>
+      <c r="M50">
+        <v>12.3567024</v>
+      </c>
+      <c r="N50">
+        <v>16.2032976</v>
+      </c>
+      <c r="O50">
+        <v>4.0508244</v>
+      </c>
+      <c r="P50">
+        <v>12.1524732</v>
+      </c>
+      <c r="Q50">
+        <v>38.5924732</v>
+      </c>
+      <c r="R50">
+        <v>0.923076923076923</v>
+      </c>
+      <c r="S50">
+        <v>0.1476135738260839</v>
+      </c>
+      <c r="T50">
+        <v>1.986863604509908</v>
+      </c>
+      <c r="U50">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V50">
+        <v>0.25</v>
+      </c>
+      <c r="W50">
+        <v>0.056175</v>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y50">
+        <v>2.311296256515816</v>
+      </c>
+      <c r="Z50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>0.49</v>
+      </c>
+      <c r="B51">
+        <v>0.1037360610645933</v>
+      </c>
+      <c r="C51">
+        <v>153.3292687624347</v>
+      </c>
+      <c r="D51">
+        <v>264.5422687624347</v>
+      </c>
+      <c r="E51">
+        <v>76.31299999999999</v>
+      </c>
+      <c r="F51">
+        <v>168.413</v>
+      </c>
+      <c r="G51">
+        <v>57.2</v>
+      </c>
+      <c r="H51">
+        <v>251.6</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>55</v>
+      </c>
+      <c r="K51">
+        <v>26.44</v>
+      </c>
+      <c r="L51">
+        <v>28.56</v>
+      </c>
+      <c r="M51">
+        <v>12.6141337</v>
+      </c>
+      <c r="N51">
+        <v>15.9458663</v>
+      </c>
+      <c r="O51">
+        <v>3.986466575</v>
+      </c>
+      <c r="P51">
+        <v>11.959399725</v>
+      </c>
+      <c r="Q51">
+        <v>38.399399725</v>
+      </c>
+      <c r="R51">
+        <v>0.9607843137254901</v>
+      </c>
+      <c r="S51">
+        <v>0.1494319824795946</v>
+      </c>
+      <c r="T51">
+        <v>2.020066539077253</v>
+      </c>
+      <c r="U51">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V51">
+        <v>0.25</v>
+      </c>
+      <c r="W51">
+        <v>0.056175</v>
+      </c>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y51">
+        <v>2.264126945158351</v>
+      </c>
+      <c r="Z51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>0.5</v>
+      </c>
+      <c r="B52">
+        <v>0.1037490637396229</v>
+      </c>
+      <c r="C52">
+        <v>149.8393079196715</v>
+      </c>
+      <c r="D52">
+        <v>264.4893079196715</v>
+      </c>
+      <c r="E52">
+        <v>79.75</v>
+      </c>
+      <c r="F52">
+        <v>171.85</v>
+      </c>
+      <c r="G52">
+        <v>57.2</v>
+      </c>
+      <c r="H52">
+        <v>251.6</v>
+      </c>
+      <c r="I52">
+        <v>0</v>
+      </c>
+      <c r="J52">
+        <v>55</v>
+      </c>
+      <c r="K52">
+        <v>26.44</v>
+      </c>
+      <c r="L52">
+        <v>28.56</v>
+      </c>
+      <c r="M52">
+        <v>12.871565</v>
+      </c>
+      <c r="N52">
+        <v>15.688435</v>
+      </c>
+      <c r="O52">
+        <v>3.92210875</v>
+      </c>
+      <c r="P52">
+        <v>11.76632625</v>
+      </c>
+      <c r="Q52">
+        <v>38.20632625</v>
+      </c>
+      <c r="R52">
         <v>1</v>
       </c>
-      <c r="U3">
-        <v>174.5</v>
-      </c>
-      <c r="V3">
-        <v>0.3949751018560435</v>
-      </c>
-      <c r="W3">
-        <v>-0.08024691358024691</v>
-      </c>
-      <c r="X3">
-        <v>0.1390986395106163</v>
-      </c>
-      <c r="Y3">
-        <v>-0.2193455530908632</v>
-      </c>
-      <c r="Z3">
-        <v>36.52112676056331</v>
-      </c>
-      <c r="AA3">
-        <v>-0.5533199195171015</v>
-      </c>
-      <c r="AB3">
-        <v>0.1244548244130002</v>
-      </c>
-      <c r="AC3">
-        <v>-0.6777747439301017</v>
-      </c>
-      <c r="AD3">
-        <v>77.5</v>
-      </c>
-      <c r="AE3">
-        <v>0</v>
-      </c>
-      <c r="AF3">
-        <v>77.5</v>
-      </c>
-      <c r="AG3">
-        <v>-97</v>
-      </c>
-      <c r="AH3">
-        <v>0.1492393606778356</v>
-      </c>
-      <c r="AI3">
-        <v>0.09179201705554899</v>
-      </c>
-      <c r="AJ3">
-        <v>-0.281322505800464</v>
-      </c>
-      <c r="AK3">
-        <v>-0.1448193490594207</v>
-      </c>
-      <c r="AL3">
-        <v>4.9</v>
-      </c>
-      <c r="AM3">
-        <v>-3.93</v>
-      </c>
-      <c r="AN3">
-        <v>26.36054421768707</v>
-      </c>
-      <c r="AO3">
-        <v>-5.612244897959183</v>
-      </c>
-      <c r="AP3">
-        <v>-32.99319727891157</v>
-      </c>
-      <c r="AQ3">
-        <v>6.997455470737914</v>
+      <c r="S52">
+        <v>0.1513231274792458</v>
+      </c>
+      <c r="T52">
+        <v>2.054597591027291</v>
+      </c>
+      <c r="U52">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V52">
+        <v>0.25</v>
+      </c>
+      <c r="W52">
+        <v>0.056175</v>
+      </c>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y52">
+        <v>2.218844406255184</v>
+      </c>
+      <c r="Z52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53">
+        <v>0.51</v>
+      </c>
+      <c r="B53">
+        <v>0.1037620664146526</v>
+      </c>
+      <c r="C53">
+        <v>146.3493682779774</v>
+      </c>
+      <c r="D53">
+        <v>264.4363682779774</v>
+      </c>
+      <c r="E53">
+        <v>83.18700000000001</v>
+      </c>
+      <c r="F53">
+        <v>175.287</v>
+      </c>
+      <c r="G53">
+        <v>57.2</v>
+      </c>
+      <c r="H53">
+        <v>251.6</v>
+      </c>
+      <c r="I53">
+        <v>0</v>
+      </c>
+      <c r="J53">
+        <v>55</v>
+      </c>
+      <c r="K53">
+        <v>26.44</v>
+      </c>
+      <c r="L53">
+        <v>28.56</v>
+      </c>
+      <c r="M53">
+        <v>13.1289963</v>
+      </c>
+      <c r="N53">
+        <v>15.4310037</v>
+      </c>
+      <c r="O53">
+        <v>3.857750925</v>
+      </c>
+      <c r="P53">
+        <v>11.573252775</v>
+      </c>
+      <c r="Q53">
+        <v>38.013252775</v>
+      </c>
+      <c r="R53">
+        <v>1.040816326530612</v>
+      </c>
+      <c r="S53">
+        <v>0.1532914620707195</v>
+      </c>
+      <c r="T53">
+        <v>2.090538073669169</v>
+      </c>
+      <c r="U53">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V53">
+        <v>0.25</v>
+      </c>
+      <c r="W53">
+        <v>0.056175</v>
+      </c>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y53">
+        <v>2.175337653191356</v>
+      </c>
+      <c r="Z53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54">
+        <v>0.52</v>
+      </c>
+      <c r="B54">
+        <v>0.1037750690896822</v>
+      </c>
+      <c r="C54">
+        <v>142.8594498246243</v>
+      </c>
+      <c r="D54">
+        <v>264.3834498246243</v>
+      </c>
+      <c r="E54">
+        <v>86.624</v>
+      </c>
+      <c r="F54">
+        <v>178.724</v>
+      </c>
+      <c r="G54">
+        <v>57.2</v>
+      </c>
+      <c r="H54">
+        <v>251.6</v>
+      </c>
+      <c r="I54">
+        <v>0</v>
+      </c>
+      <c r="J54">
+        <v>55</v>
+      </c>
+      <c r="K54">
+        <v>26.44</v>
+      </c>
+      <c r="L54">
+        <v>28.56</v>
+      </c>
+      <c r="M54">
+        <v>13.3864276</v>
+      </c>
+      <c r="N54">
+        <v>15.1735724</v>
+      </c>
+      <c r="O54">
+        <v>3.7933931</v>
+      </c>
+      <c r="P54">
+        <v>11.3801793</v>
+      </c>
+      <c r="Q54">
+        <v>37.82017930000001</v>
+      </c>
+      <c r="R54">
+        <v>1.083333333333333</v>
+      </c>
+      <c r="S54">
+        <v>0.1553418106035046</v>
+      </c>
+      <c r="T54">
+        <v>2.127976076421123</v>
+      </c>
+      <c r="U54">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V54">
+        <v>0.25</v>
+      </c>
+      <c r="W54">
+        <v>0.056175</v>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y54">
+        <v>2.133504236783831</v>
+      </c>
+      <c r="Z54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55">
+        <v>0.53</v>
+      </c>
+      <c r="B55">
+        <v>0.1037880717647119</v>
+      </c>
+      <c r="C55">
+        <v>139.3695525468942</v>
+      </c>
+      <c r="D55">
+        <v>264.3305525468942</v>
+      </c>
+      <c r="E55">
+        <v>90.06100000000001</v>
+      </c>
+      <c r="F55">
+        <v>182.161</v>
+      </c>
+      <c r="G55">
+        <v>57.2</v>
+      </c>
+      <c r="H55">
+        <v>251.6</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>55</v>
+      </c>
+      <c r="K55">
+        <v>26.44</v>
+      </c>
+      <c r="L55">
+        <v>28.56</v>
+      </c>
+      <c r="M55">
+        <v>13.6438589</v>
+      </c>
+      <c r="N55">
+        <v>14.9161411</v>
+      </c>
+      <c r="O55">
+        <v>3.729035275</v>
+      </c>
+      <c r="P55">
+        <v>11.187105825</v>
+      </c>
+      <c r="Q55">
+        <v>37.627105825</v>
+      </c>
+      <c r="R55">
+        <v>1.127659574468085</v>
+      </c>
+      <c r="S55">
+        <v>0.1574794080100252</v>
+      </c>
+      <c r="T55">
+        <v>2.167007185673162</v>
+      </c>
+      <c r="U55">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V55">
+        <v>0.25</v>
+      </c>
+      <c r="W55">
+        <v>0.056175</v>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y55">
+        <v>2.093249439863381</v>
+      </c>
+      <c r="Z55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56">
+        <v>0.54</v>
+      </c>
+      <c r="B56">
+        <v>0.1038010744397415</v>
+      </c>
+      <c r="C56">
+        <v>135.8796764320791</v>
+      </c>
+      <c r="D56">
+        <v>264.2776764320791</v>
+      </c>
+      <c r="E56">
+        <v>93.49800000000002</v>
+      </c>
+      <c r="F56">
+        <v>185.598</v>
+      </c>
+      <c r="G56">
+        <v>57.2</v>
+      </c>
+      <c r="H56">
+        <v>251.6</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>55</v>
+      </c>
+      <c r="K56">
+        <v>26.44</v>
+      </c>
+      <c r="L56">
+        <v>28.56</v>
+      </c>
+      <c r="M56">
+        <v>13.9012902</v>
+      </c>
+      <c r="N56">
+        <v>14.6587098</v>
+      </c>
+      <c r="O56">
+        <v>3.66467745</v>
+      </c>
+      <c r="P56">
+        <v>10.99403235</v>
+      </c>
+      <c r="Q56">
+        <v>37.43403235</v>
+      </c>
+      <c r="R56">
+        <v>1.173913043478261</v>
+      </c>
+      <c r="S56">
+        <v>0.1597099444342207</v>
+      </c>
+      <c r="T56">
+        <v>2.207735299675289</v>
+      </c>
+      <c r="U56">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V56">
+        <v>0.25</v>
+      </c>
+      <c r="W56">
+        <v>0.056175</v>
+      </c>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y56">
+        <v>2.054485561347392</v>
+      </c>
+      <c r="Z56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57">
+        <v>0.55</v>
+      </c>
+      <c r="B57">
+        <v>0.1038140771147712</v>
+      </c>
+      <c r="C57">
+        <v>132.3898214674817</v>
+      </c>
+      <c r="D57">
+        <v>264.2248214674817</v>
+      </c>
+      <c r="E57">
+        <v>96.935</v>
+      </c>
+      <c r="F57">
+        <v>189.035</v>
+      </c>
+      <c r="G57">
+        <v>57.2</v>
+      </c>
+      <c r="H57">
+        <v>251.6</v>
+      </c>
+      <c r="I57">
+        <v>0</v>
+      </c>
+      <c r="J57">
+        <v>55</v>
+      </c>
+      <c r="K57">
+        <v>26.44</v>
+      </c>
+      <c r="L57">
+        <v>28.56</v>
+      </c>
+      <c r="M57">
+        <v>14.1587215</v>
+      </c>
+      <c r="N57">
+        <v>14.4012785</v>
+      </c>
+      <c r="O57">
+        <v>3.600319625</v>
+      </c>
+      <c r="P57">
+        <v>10.800958875</v>
+      </c>
+      <c r="Q57">
+        <v>37.240958875</v>
+      </c>
+      <c r="R57">
+        <v>1.222222222222223</v>
+      </c>
+      <c r="S57">
+        <v>0.1620396158106026</v>
+      </c>
+      <c r="T57">
+        <v>2.25027355207751</v>
+      </c>
+      <c r="U57">
+        <v>0.07489999999999999</v>
+      </c>
+      <c r="V57">
+        <v>0.25</v>
+      </c>
+      <c r="W57">
+        <v>0.056175</v>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>B2/B</t>
+        </is>
+      </c>
+      <c r="Y57">
+        <v>2.017131278413803</v>
+      </c>
+      <c r="Z57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="B58">
+        <v>0.1106730797898008</v>
+      </c>
+      <c r="C58">
+        <v>103.7372781436813</v>
+      </c>
+      <c r="D58">
+        <v>239.0092781436813</v>
+      </c>
+      <c r="E58">
+        <v>100.372</v>
+      </c>
+      <c r="F58">
+        <v>192.472</v>
+      </c>
+      <c r="G58">
+        <v>57.2</v>
+      </c>
+      <c r="H58">
+        <v>251.6</v>
+      </c>
+      <c r="I58">
+        <v>0</v>
+      </c>
+      <c r="J58">
+        <v>55</v>
+      </c>
+      <c r="K58">
+        <v>26.44</v>
+      </c>
+      <c r="L58">
+        <v>28.56</v>
+      </c>
+      <c r="M58">
+        <v>17.5534464</v>
+      </c>
+      <c r="N58">
+        <v>11.0065536</v>
+      </c>
+      <c r="O58">
+        <v>2.751638399999999</v>
+      </c>
+      <c r="P58">
+        <v>8.254915199999997</v>
+      </c>
+      <c r="Q58">
+        <v>34.6949152</v>
+      </c>
+      <c r="R58">
+        <v>1.272727272727273</v>
+      </c>
+      <c r="S58">
+        <v>0.1644751813404564</v>
+      </c>
+      <c r="T58">
+        <v>2.294745361407105</v>
+      </c>
+      <c r="U58">
+        <v>0.0912</v>
+      </c>
+      <c r="V58">
+        <v>0.25</v>
+      </c>
+      <c r="W58">
+        <v>0.0684</v>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y58">
+        <v>1.627030917415739</v>
+      </c>
+      <c r="Z58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59">
+        <v>0.5700000000000001</v>
+      </c>
+      <c r="B59">
+        <v>0.1108083324648305</v>
+      </c>
+      <c r="C59">
+        <v>99.85134892786269</v>
+      </c>
+      <c r="D59">
+        <v>238.5603489278627</v>
+      </c>
+      <c r="E59">
+        <v>103.809</v>
+      </c>
+      <c r="F59">
+        <v>195.909</v>
+      </c>
+      <c r="G59">
+        <v>57.2</v>
+      </c>
+      <c r="H59">
+        <v>251.6</v>
+      </c>
+      <c r="I59">
+        <v>0</v>
+      </c>
+      <c r="J59">
+        <v>55</v>
+      </c>
+      <c r="K59">
+        <v>26.44</v>
+      </c>
+      <c r="L59">
+        <v>28.56</v>
+      </c>
+      <c r="M59">
+        <v>17.8669008</v>
+      </c>
+      <c r="N59">
+        <v>10.6930992</v>
+      </c>
+      <c r="O59">
+        <v>2.673274799999999</v>
+      </c>
+      <c r="P59">
+        <v>8.019824399999997</v>
+      </c>
+      <c r="Q59">
+        <v>34.4598244</v>
+      </c>
+      <c r="R59">
+        <v>1.325581395348838</v>
+      </c>
+      <c r="S59">
+        <v>0.1670240289879778</v>
+      </c>
+      <c r="T59">
+        <v>2.341285626984588</v>
+      </c>
+      <c r="U59">
+        <v>0.0912</v>
+      </c>
+      <c r="V59">
+        <v>0.25</v>
+      </c>
+      <c r="W59">
+        <v>0.0684</v>
+      </c>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y59">
+        <v>1.598486515355813</v>
+      </c>
+      <c r="Z59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60">
+        <v>0.58</v>
+      </c>
+      <c r="B60">
+        <v>0.1109435851398601</v>
+      </c>
+      <c r="C60">
+        <v>95.96710299066748</v>
+      </c>
+      <c r="D60">
+        <v>238.1131029906675</v>
+      </c>
+      <c r="E60">
+        <v>107.246</v>
+      </c>
+      <c r="F60">
+        <v>199.346</v>
+      </c>
+      <c r="G60">
+        <v>57.2</v>
+      </c>
+      <c r="H60">
+        <v>251.6</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="J60">
+        <v>55</v>
+      </c>
+      <c r="K60">
+        <v>26.44</v>
+      </c>
+      <c r="L60">
+        <v>28.56</v>
+      </c>
+      <c r="M60">
+        <v>18.1803552</v>
+      </c>
+      <c r="N60">
+        <v>10.3796448</v>
+      </c>
+      <c r="O60">
+        <v>2.5949112</v>
+      </c>
+      <c r="P60">
+        <v>7.784733600000001</v>
+      </c>
+      <c r="Q60">
+        <v>34.2247336</v>
+      </c>
+      <c r="R60">
+        <v>1.380952380952381</v>
+      </c>
+      <c r="S60">
+        <v>0.1696942503330002</v>
+      </c>
+      <c r="T60">
+        <v>2.390042095684808</v>
+      </c>
+      <c r="U60">
+        <v>0.0912</v>
+      </c>
+      <c r="V60">
+        <v>0.25</v>
+      </c>
+      <c r="W60">
+        <v>0.0684</v>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y60">
+        <v>1.570926403022093</v>
+      </c>
+      <c r="Z60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61">
+        <v>0.59</v>
+      </c>
+      <c r="B61">
+        <v>0.1110788378148898</v>
+      </c>
+      <c r="C61">
+        <v>92.08453088252739</v>
+      </c>
+      <c r="D61">
+        <v>237.6675308825274</v>
+      </c>
+      <c r="E61">
+        <v>110.683</v>
+      </c>
+      <c r="F61">
+        <v>202.783</v>
+      </c>
+      <c r="G61">
+        <v>57.2</v>
+      </c>
+      <c r="H61">
+        <v>251.6</v>
+      </c>
+      <c r="I61">
+        <v>0</v>
+      </c>
+      <c r="J61">
+        <v>55</v>
+      </c>
+      <c r="K61">
+        <v>26.44</v>
+      </c>
+      <c r="L61">
+        <v>28.56</v>
+      </c>
+      <c r="M61">
+        <v>18.4938096</v>
+      </c>
+      <c r="N61">
+        <v>10.0661904</v>
+      </c>
+      <c r="O61">
+        <v>2.5165476</v>
+      </c>
+      <c r="P61">
+        <v>7.5496428</v>
+      </c>
+      <c r="Q61">
+        <v>33.9896428</v>
+      </c>
+      <c r="R61">
+        <v>1.439024390243902</v>
+      </c>
+      <c r="S61">
+        <v>0.1724947263777799</v>
+      </c>
+      <c r="T61">
+        <v>2.441176928711869</v>
+      </c>
+      <c r="U61">
+        <v>0.0912</v>
+      </c>
+      <c r="V61">
+        <v>0.25</v>
+      </c>
+      <c r="W61">
+        <v>0.0684</v>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y61">
+        <v>1.54430053178443</v>
+      </c>
+      <c r="Z61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62">
+        <v>0.6</v>
+      </c>
+      <c r="B62">
+        <v>0.1112140904899194</v>
+      </c>
+      <c r="C62">
+        <v>88.20362322447252</v>
+      </c>
+      <c r="D62">
+        <v>237.2236232244725</v>
+      </c>
+      <c r="E62">
+        <v>114.12</v>
+      </c>
+      <c r="F62">
+        <v>206.22</v>
+      </c>
+      <c r="G62">
+        <v>57.2</v>
+      </c>
+      <c r="H62">
+        <v>251.6</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>55</v>
+      </c>
+      <c r="K62">
+        <v>26.44</v>
+      </c>
+      <c r="L62">
+        <v>28.56</v>
+      </c>
+      <c r="M62">
+        <v>18.807264</v>
+      </c>
+      <c r="N62">
+        <v>9.752735999999999</v>
+      </c>
+      <c r="O62">
+        <v>2.438184</v>
+      </c>
+      <c r="P62">
+        <v>7.314551999999999</v>
+      </c>
+      <c r="Q62">
+        <v>33.754552</v>
+      </c>
+      <c r="R62">
+        <v>1.5</v>
+      </c>
+      <c r="S62">
+        <v>0.1754352262247985</v>
+      </c>
+      <c r="T62">
+        <v>2.494868503390282</v>
+      </c>
+      <c r="U62">
+        <v>0.0912</v>
+      </c>
+      <c r="V62">
+        <v>0.25</v>
+      </c>
+      <c r="W62">
+        <v>0.0684</v>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>B3/B-</t>
+        </is>
+      </c>
+      <c r="Y62">
+        <v>1.518562189588023</v>
+      </c>
+      <c r="Z62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63">
+        <v>0.61</v>
+      </c>
+      <c r="B63">
+        <v>0.1456533599044237</v>
+      </c>
+      <c r="C63">
+        <v>8.308491453791191</v>
+      </c>
+      <c r="D63">
+        <v>160.7654914537912</v>
+      </c>
+      <c r="E63">
+        <v>117.557</v>
+      </c>
+      <c r="F63">
+        <v>209.657</v>
+      </c>
+      <c r="G63">
+        <v>57.2</v>
+      </c>
+      <c r="H63">
+        <v>251.6</v>
+      </c>
+      <c r="I63">
+        <v>0</v>
+      </c>
+      <c r="J63">
+        <v>55</v>
+      </c>
+      <c r="K63">
+        <v>26.44</v>
+      </c>
+      <c r="L63">
+        <v>28.56</v>
+      </c>
+      <c r="M63">
+        <v>32.8322862</v>
+      </c>
+      <c r="N63">
+        <v>-4.2722862</v>
+      </c>
+      <c r="O63">
+        <v>-1.06807155</v>
+      </c>
+      <c r="P63">
+        <v>-3.20421465</v>
+      </c>
+      <c r="Q63">
+        <v>23.23578535</v>
+      </c>
+      <c r="R63">
+        <v>1.564102564102564</v>
+      </c>
+      <c r="S63">
+        <v>0.1817981811743278</v>
+      </c>
+      <c r="T63">
+        <v>2.611051835688164</v>
+      </c>
+      <c r="U63">
+        <v>0.1566</v>
+      </c>
+      <c r="V63">
+        <v>0.2174688645349345</v>
+      </c>
+      <c r="W63">
+        <v>0.1225443758138293</v>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y63">
+        <v>0.8698754581397381</v>
+      </c>
+      <c r="Z63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64">
+        <v>0.62</v>
+      </c>
+      <c r="B64">
+        <v>0.1468313599044237</v>
+      </c>
+      <c r="C64">
+        <v>3.118465766619181</v>
+      </c>
+      <c r="D64">
+        <v>159.0124657666192</v>
+      </c>
+      <c r="E64">
+        <v>120.994</v>
+      </c>
+      <c r="F64">
+        <v>213.094</v>
+      </c>
+      <c r="G64">
+        <v>57.2</v>
+      </c>
+      <c r="H64">
+        <v>251.6</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>55</v>
+      </c>
+      <c r="K64">
+        <v>26.44</v>
+      </c>
+      <c r="L64">
+        <v>28.56</v>
+      </c>
+      <c r="M64">
+        <v>33.3705204</v>
+      </c>
+      <c r="N64">
+        <v>-4.810520400000005</v>
+      </c>
+      <c r="O64">
+        <v>-1.202630100000001</v>
+      </c>
+      <c r="P64">
+        <v>-3.607890300000004</v>
+      </c>
+      <c r="Q64">
+        <v>22.8321097</v>
+      </c>
+      <c r="R64">
+        <v>1.631578947368421</v>
+      </c>
+      <c r="S64">
+        <v>0.1855612912052312</v>
+      </c>
+      <c r="T64">
+        <v>2.679763726101011</v>
+      </c>
+      <c r="U64">
+        <v>0.1566</v>
+      </c>
+      <c r="V64">
+        <v>0.2139613022037259</v>
+      </c>
+      <c r="W64">
+        <v>0.1230936600748965</v>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y64">
+        <v>0.8558452088149034</v>
+      </c>
+      <c r="Z64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65">
+        <v>0.63</v>
+      </c>
+      <c r="B65">
+        <v>0.1480093599044237</v>
+      </c>
+      <c r="C65">
+        <v>-2.033741472366614</v>
+      </c>
+      <c r="D65">
+        <v>157.2972585276334</v>
+      </c>
+      <c r="E65">
+        <v>124.431</v>
+      </c>
+      <c r="F65">
+        <v>216.531</v>
+      </c>
+      <c r="G65">
+        <v>57.2</v>
+      </c>
+      <c r="H65">
+        <v>251.6</v>
+      </c>
+      <c r="I65">
+        <v>0</v>
+      </c>
+      <c r="J65">
+        <v>55</v>
+      </c>
+      <c r="K65">
+        <v>26.44</v>
+      </c>
+      <c r="L65">
+        <v>28.56</v>
+      </c>
+      <c r="M65">
+        <v>33.9087546</v>
+      </c>
+      <c r="N65">
+        <v>-5.348754600000003</v>
+      </c>
+      <c r="O65">
+        <v>-1.337188650000001</v>
+      </c>
+      <c r="P65">
+        <v>-4.011565950000002</v>
+      </c>
+      <c r="Q65">
+        <v>22.42843405</v>
+      </c>
+      <c r="R65">
+        <v>1.702702702702703</v>
+      </c>
+      <c r="S65">
+        <v>0.1895278125891564</v>
+      </c>
+      <c r="T65">
+        <v>2.75218977275239</v>
+      </c>
+      <c r="U65">
+        <v>0.1566</v>
+      </c>
+      <c r="V65">
+        <v>0.210565091057635</v>
+      </c>
+      <c r="W65">
+        <v>0.1236255067403744</v>
+      </c>
+      <c r="X65" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y65">
+        <v>0.84226036423054</v>
+      </c>
+      <c r="Z65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66">
+        <v>0.64</v>
+      </c>
+      <c r="B66">
+        <v>0.1491873599044237</v>
+      </c>
+      <c r="C66">
+        <v>-7.149341003200419</v>
+      </c>
+      <c r="D66">
+        <v>155.6186589967996</v>
+      </c>
+      <c r="E66">
+        <v>127.868</v>
+      </c>
+      <c r="F66">
+        <v>219.968</v>
+      </c>
+      <c r="G66">
+        <v>57.2</v>
+      </c>
+      <c r="H66">
+        <v>251.6</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>55</v>
+      </c>
+      <c r="K66">
+        <v>26.44</v>
+      </c>
+      <c r="L66">
+        <v>28.56</v>
+      </c>
+      <c r="M66">
+        <v>34.4469888</v>
+      </c>
+      <c r="N66">
+        <v>-5.886988800000001</v>
+      </c>
+      <c r="O66">
+        <v>-1.4717472</v>
+      </c>
+      <c r="P66">
+        <v>-4.415241600000001</v>
+      </c>
+      <c r="Q66">
+        <v>22.0247584</v>
+      </c>
+      <c r="R66">
+        <v>1.777777777777778</v>
+      </c>
+      <c r="S66">
+        <v>0.1937146962721885</v>
+      </c>
+      <c r="T66">
+        <v>2.828639488662178</v>
+      </c>
+      <c r="U66">
+        <v>0.1566</v>
+      </c>
+      <c r="V66">
+        <v>0.2072750115098594</v>
+      </c>
+      <c r="W66">
+        <v>0.124140733197556</v>
+      </c>
+      <c r="X66" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y66">
+        <v>0.8291000460394378</v>
+      </c>
+      <c r="Z66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67">
+        <v>0.65</v>
+      </c>
+      <c r="B67">
+        <v>0.1503653599044237</v>
+      </c>
+      <c r="C67">
+        <v>-12.22949242990924</v>
+      </c>
+      <c r="D67">
+        <v>153.9755075700908</v>
+      </c>
+      <c r="E67">
+        <v>131.305</v>
+      </c>
+      <c r="F67">
+        <v>223.405</v>
+      </c>
+      <c r="G67">
+        <v>57.2</v>
+      </c>
+      <c r="H67">
+        <v>251.6</v>
+      </c>
+      <c r="I67">
+        <v>0</v>
+      </c>
+      <c r="J67">
+        <v>55</v>
+      </c>
+      <c r="K67">
+        <v>26.44</v>
+      </c>
+      <c r="L67">
+        <v>28.56</v>
+      </c>
+      <c r="M67">
+        <v>34.985223</v>
+      </c>
+      <c r="N67">
+        <v>-6.425223000000006</v>
+      </c>
+      <c r="O67">
+        <v>-1.606305750000002</v>
+      </c>
+      <c r="P67">
+        <v>-4.818917250000005</v>
+      </c>
+      <c r="Q67">
+        <v>21.62108275</v>
+      </c>
+      <c r="R67">
+        <v>1.857142857142857</v>
+      </c>
+      <c r="S67">
+        <v>0.1981408304513939</v>
+      </c>
+      <c r="T67">
+        <v>2.909457759766812</v>
+      </c>
+      <c r="U67">
+        <v>0.1566</v>
+      </c>
+      <c r="V67">
+        <v>0.2040861651789385</v>
+      </c>
+      <c r="W67">
+        <v>0.1246401065329782</v>
+      </c>
+      <c r="X67" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y67">
+        <v>0.8163446607157541</v>
+      </c>
+      <c r="Z67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.66</v>
+      </c>
+      <c r="B68">
+        <v>0.1515433599044237</v>
+      </c>
+      <c r="C68">
+        <v>-17.27530689198781</v>
+      </c>
+      <c r="D68">
+        <v>152.3666931080122</v>
+      </c>
+      <c r="E68">
+        <v>134.742</v>
+      </c>
+      <c r="F68">
+        <v>226.842</v>
+      </c>
+      <c r="G68">
+        <v>57.2</v>
+      </c>
+      <c r="H68">
+        <v>251.6</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>55</v>
+      </c>
+      <c r="K68">
+        <v>26.44</v>
+      </c>
+      <c r="L68">
+        <v>28.56</v>
+      </c>
+      <c r="M68">
+        <v>35.5234572</v>
+      </c>
+      <c r="N68">
+        <v>-6.963457200000004</v>
+      </c>
+      <c r="O68">
+        <v>-1.740864300000001</v>
+      </c>
+      <c r="P68">
+        <v>-5.222592900000003</v>
+      </c>
+      <c r="Q68">
+        <v>21.2174071</v>
+      </c>
+      <c r="R68">
+        <v>1.941176470588236</v>
+      </c>
+      <c r="S68">
+        <v>0.2028273254646702</v>
+      </c>
+      <c r="T68">
+        <v>2.995030046818777</v>
+      </c>
+      <c r="U68">
+        <v>0.1566</v>
+      </c>
+      <c r="V68">
+        <v>0.2009939505550152</v>
+      </c>
+      <c r="W68">
+        <v>0.1251243473430846</v>
+      </c>
+      <c r="X68" t="inlineStr">
+        <is>
+          <t>Ca2/CC</t>
+        </is>
+      </c>
+      <c r="Y68">
+        <v>0.8039758022200608</v>
+      </c>
+      <c r="Z68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.67</v>
+      </c>
+      <c r="B69">
+        <v>0.1898277697369619</v>
+      </c>
+      <c r="C69">
+        <v>-59.33612378298236</v>
+      </c>
+      <c r="D69">
+        <v>113.7428762170176</v>
+      </c>
+      <c r="E69">
+        <v>138.179</v>
+      </c>
+      <c r="F69">
+        <v>230.279</v>
+      </c>
+      <c r="G69">
+        <v>57.2</v>
+      </c>
+      <c r="H69">
+        <v>251.6</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>55</v>
+      </c>
+      <c r="K69">
+        <v>26.44</v>
+      </c>
+      <c r="L69">
+        <v>28.56</v>
+      </c>
+      <c r="M69">
+        <v>48.08225520000001</v>
+      </c>
+      <c r="N69">
+        <v>-19.52225520000001</v>
+      </c>
+      <c r="O69">
+        <v>-4.880563800000002</v>
+      </c>
+      <c r="P69">
+        <v>-14.64169140000001</v>
+      </c>
+      <c r="Q69">
+        <v>11.7983086</v>
+      </c>
+      <c r="R69">
+        <v>2.030303030303031</v>
+      </c>
+      <c r="S69">
+        <v>0.2142596984561394</v>
+      </c>
+      <c r="T69">
+        <v>3.203777586406411</v>
+      </c>
+      <c r="U69">
+        <v>0.2088</v>
+      </c>
+      <c r="V69">
+        <v>0.1484955306339291</v>
+      </c>
+      <c r="W69">
+        <v>0.1777941332036356</v>
+      </c>
+      <c r="X69" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y69">
+        <v>0.5939821225357166</v>
+      </c>
+      <c r="Z69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.68</v>
+      </c>
+      <c r="B70">
+        <v>0.1915277697369619</v>
+      </c>
+      <c r="C70">
+        <v>-64.03918620176813</v>
+      </c>
+      <c r="D70">
+        <v>112.4768137982319</v>
+      </c>
+      <c r="E70">
+        <v>141.616</v>
+      </c>
+      <c r="F70">
+        <v>233.716</v>
+      </c>
+      <c r="G70">
+        <v>57.2</v>
+      </c>
+      <c r="H70">
+        <v>251.6</v>
+      </c>
+      <c r="I70">
+        <v>0</v>
+      </c>
+      <c r="J70">
+        <v>55</v>
+      </c>
+      <c r="K70">
+        <v>26.44</v>
+      </c>
+      <c r="L70">
+        <v>28.56</v>
+      </c>
+      <c r="M70">
+        <v>48.7999008</v>
+      </c>
+      <c r="N70">
+        <v>-20.2399008</v>
+      </c>
+      <c r="O70">
+        <v>-5.059975200000001</v>
+      </c>
+      <c r="P70">
+        <v>-15.1799256</v>
+      </c>
+      <c r="Q70">
+        <v>11.2600744</v>
+      </c>
+      <c r="R70">
+        <v>2.125</v>
+      </c>
+      <c r="S70">
+        <v>0.2197428140328938</v>
+      </c>
+      <c r="T70">
+        <v>3.303895635981611</v>
+      </c>
+      <c r="U70">
+        <v>0.2088</v>
+      </c>
+      <c r="V70">
+        <v>0.146311772830489</v>
+      </c>
+      <c r="W70">
+        <v>0.1782501018329939</v>
+      </c>
+      <c r="X70" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y70">
+        <v>0.5852470913219561</v>
+      </c>
+      <c r="Z70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.6900000000000001</v>
+      </c>
+      <c r="B71">
+        <v>0.1932277697369619</v>
+      </c>
+      <c r="C71">
+        <v>-68.7143740211136</v>
+      </c>
+      <c r="D71">
+        <v>111.2386259788864</v>
+      </c>
+      <c r="E71">
+        <v>145.053</v>
+      </c>
+      <c r="F71">
+        <v>237.153</v>
+      </c>
+      <c r="G71">
+        <v>57.2</v>
+      </c>
+      <c r="H71">
+        <v>251.6</v>
+      </c>
+      <c r="I71">
+        <v>0</v>
+      </c>
+      <c r="J71">
+        <v>55</v>
+      </c>
+      <c r="K71">
+        <v>26.44</v>
+      </c>
+      <c r="L71">
+        <v>28.56</v>
+      </c>
+      <c r="M71">
+        <v>49.51754640000001</v>
+      </c>
+      <c r="N71">
+        <v>-20.95754640000001</v>
+      </c>
+      <c r="O71">
+        <v>-5.239386600000002</v>
+      </c>
+      <c r="P71">
+        <v>-15.71815980000001</v>
+      </c>
+      <c r="Q71">
+        <v>10.7218402</v>
+      </c>
+      <c r="R71">
+        <v>2.225806451612904</v>
+      </c>
+      <c r="S71">
+        <v>0.2255796790016968</v>
+      </c>
+      <c r="T71">
+        <v>3.410472914561663</v>
+      </c>
+      <c r="U71">
+        <v>0.2088</v>
+      </c>
+      <c r="V71">
+        <v>0.1441913123546848</v>
+      </c>
+      <c r="W71">
+        <v>0.1786928539803418</v>
+      </c>
+      <c r="X71" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y71">
+        <v>0.5767652494187392</v>
+      </c>
+      <c r="Z71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.7000000000000001</v>
+      </c>
+      <c r="B72">
+        <v>0.1949277697369619</v>
+      </c>
+      <c r="C72">
+        <v>-73.36259778023538</v>
+      </c>
+      <c r="D72">
+        <v>110.0274022197646</v>
+      </c>
+      <c r="E72">
+        <v>148.49</v>
+      </c>
+      <c r="F72">
+        <v>240.59</v>
+      </c>
+      <c r="G72">
+        <v>57.2</v>
+      </c>
+      <c r="H72">
+        <v>251.6</v>
+      </c>
+      <c r="I72">
+        <v>0</v>
+      </c>
+      <c r="J72">
+        <v>55</v>
+      </c>
+      <c r="K72">
+        <v>26.44</v>
+      </c>
+      <c r="L72">
+        <v>28.56</v>
+      </c>
+      <c r="M72">
+        <v>50.235192</v>
+      </c>
+      <c r="N72">
+        <v>-21.67519200000001</v>
+      </c>
+      <c r="O72">
+        <v>-5.418798000000002</v>
+      </c>
+      <c r="P72">
+        <v>-16.256394</v>
+      </c>
+      <c r="Q72">
+        <v>10.183606</v>
+      </c>
+      <c r="R72">
+        <v>2.333333333333334</v>
+      </c>
+      <c r="S72">
+        <v>0.2318056683017534</v>
+      </c>
+      <c r="T72">
+        <v>3.524155345047052</v>
+      </c>
+      <c r="U72">
+        <v>0.2088</v>
+      </c>
+      <c r="V72">
+        <v>0.1421314364639036</v>
+      </c>
+      <c r="W72">
+        <v>0.1791229560663369</v>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y72">
+        <v>0.5685257458556144</v>
+      </c>
+      <c r="Z72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.71</v>
+      </c>
+      <c r="B73">
+        <v>0.1966277697369618</v>
+      </c>
+      <c r="C73">
+        <v>-77.98472878782252</v>
+      </c>
+      <c r="D73">
+        <v>108.8422712121775</v>
+      </c>
+      <c r="E73">
+        <v>151.927</v>
+      </c>
+      <c r="F73">
+        <v>244.027</v>
+      </c>
+      <c r="G73">
+        <v>57.2</v>
+      </c>
+      <c r="H73">
+        <v>251.6</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>55</v>
+      </c>
+      <c r="K73">
+        <v>26.44</v>
+      </c>
+      <c r="L73">
+        <v>28.56</v>
+      </c>
+      <c r="M73">
+        <v>50.9528376</v>
+      </c>
+      <c r="N73">
+        <v>-22.3928376</v>
+      </c>
+      <c r="O73">
+        <v>-5.598209400000001</v>
+      </c>
+      <c r="P73">
+        <v>-16.7946282</v>
+      </c>
+      <c r="Q73">
+        <v>9.645371799999999</v>
+      </c>
+      <c r="R73">
+        <v>2.448275862068965</v>
+      </c>
+      <c r="S73">
+        <v>0.2384610361742276</v>
+      </c>
+      <c r="T73">
+        <v>3.645677943152121</v>
+      </c>
+      <c r="U73">
+        <v>0.2088</v>
+      </c>
+      <c r="V73">
+        <v>0.1401295852461022</v>
+      </c>
+      <c r="W73">
+        <v>0.1795409426006139</v>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y73">
+        <v>0.5605183409844086</v>
+      </c>
+      <c r="Z73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.72</v>
+      </c>
+      <c r="B74">
+        <v>0.1983277697369619</v>
+      </c>
+      <c r="C74">
+        <v>-82.5816012123276</v>
+      </c>
+      <c r="D74">
+        <v>107.6823987876724</v>
+      </c>
+      <c r="E74">
+        <v>155.364</v>
+      </c>
+      <c r="F74">
+        <v>247.464</v>
+      </c>
+      <c r="G74">
+        <v>57.2</v>
+      </c>
+      <c r="H74">
+        <v>251.6</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>55</v>
+      </c>
+      <c r="K74">
+        <v>26.44</v>
+      </c>
+      <c r="L74">
+        <v>28.56</v>
+      </c>
+      <c r="M74">
+        <v>51.6704832</v>
+      </c>
+      <c r="N74">
+        <v>-23.1104832</v>
+      </c>
+      <c r="O74">
+        <v>-5.7776208</v>
+      </c>
+      <c r="P74">
+        <v>-17.3328624</v>
+      </c>
+      <c r="Q74">
+        <v>9.107137600000001</v>
+      </c>
+      <c r="R74">
+        <v>2.571428571428571</v>
+      </c>
+      <c r="S74">
+        <v>0.2455917874661643</v>
+      </c>
+      <c r="T74">
+        <v>3.775880726836126</v>
+      </c>
+      <c r="U74">
+        <v>0.2088</v>
+      </c>
+      <c r="V74">
+        <v>0.138183341006573</v>
+      </c>
+      <c r="W74">
+        <v>0.1799473183978276</v>
+      </c>
+      <c r="X74" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y74">
+        <v>0.5527333640262919</v>
+      </c>
+      <c r="Z74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.73</v>
+      </c>
+      <c r="B75">
+        <v>0.2000277697369618</v>
+      </c>
+      <c r="C75">
+        <v>-87.15401404001668</v>
+      </c>
+      <c r="D75">
+        <v>106.5469859599833</v>
+      </c>
+      <c r="E75">
+        <v>158.801</v>
+      </c>
+      <c r="F75">
+        <v>250.901</v>
+      </c>
+      <c r="G75">
+        <v>57.2</v>
+      </c>
+      <c r="H75">
+        <v>251.6</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>55</v>
+      </c>
+      <c r="K75">
+        <v>26.44</v>
+      </c>
+      <c r="L75">
+        <v>28.56</v>
+      </c>
+      <c r="M75">
+        <v>52.3881288</v>
+      </c>
+      <c r="N75">
+        <v>-23.8281288</v>
+      </c>
+      <c r="O75">
+        <v>-5.9570322</v>
+      </c>
+      <c r="P75">
+        <v>-17.8710966</v>
+      </c>
+      <c r="Q75">
+        <v>8.568903400000004</v>
+      </c>
+      <c r="R75">
+        <v>2.703703703703703</v>
+      </c>
+      <c r="S75">
+        <v>0.2532507425575037</v>
+      </c>
+      <c r="T75">
+        <v>3.91572816116339</v>
+      </c>
+      <c r="U75">
+        <v>0.2088</v>
+      </c>
+      <c r="V75">
+        <v>0.1362904185270309</v>
+      </c>
+      <c r="W75">
+        <v>0.180342560611556</v>
+      </c>
+      <c r="X75" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y75">
+        <v>0.5451616741081236</v>
+      </c>
+      <c r="Z75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.74</v>
+      </c>
+      <c r="B76">
+        <v>0.2017277697369619</v>
+      </c>
+      <c r="C76">
+        <v>-91.70273291043637</v>
+      </c>
+      <c r="D76">
+        <v>105.4352670895636</v>
+      </c>
+      <c r="E76">
+        <v>162.238</v>
+      </c>
+      <c r="F76">
+        <v>254.338</v>
+      </c>
+      <c r="G76">
+        <v>57.2</v>
+      </c>
+      <c r="H76">
+        <v>251.6</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>55</v>
+      </c>
+      <c r="K76">
+        <v>26.44</v>
+      </c>
+      <c r="L76">
+        <v>28.56</v>
+      </c>
+      <c r="M76">
+        <v>53.1057744</v>
+      </c>
+      <c r="N76">
+        <v>-24.5457744</v>
+      </c>
+      <c r="O76">
+        <v>-6.136443600000001</v>
+      </c>
+      <c r="P76">
+        <v>-18.4093308</v>
+      </c>
+      <c r="Q76">
+        <v>8.030669199999998</v>
+      </c>
+      <c r="R76">
+        <v>2.846153846153846</v>
+      </c>
+      <c r="S76">
+        <v>0.2614988480404846</v>
+      </c>
+      <c r="T76">
+        <v>4.066333090438905</v>
+      </c>
+      <c r="U76">
+        <v>0.2088</v>
+      </c>
+      <c r="V76">
+        <v>0.1344486561145034</v>
+      </c>
+      <c r="W76">
+        <v>0.1807271206032917</v>
+      </c>
+      <c r="X76" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y76">
+        <v>0.5377946244580136</v>
+      </c>
+      <c r="Z76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.75</v>
+      </c>
+      <c r="B77">
+        <v>0.2034277697369618</v>
+      </c>
+      <c r="C77">
+        <v>-96.22849183815941</v>
+      </c>
+      <c r="D77">
+        <v>104.3465081618406</v>
+      </c>
+      <c r="E77">
+        <v>165.675</v>
+      </c>
+      <c r="F77">
+        <v>257.775</v>
+      </c>
+      <c r="G77">
+        <v>57.2</v>
+      </c>
+      <c r="H77">
+        <v>251.6</v>
+      </c>
+      <c r="I77">
+        <v>0</v>
+      </c>
+      <c r="J77">
+        <v>55</v>
+      </c>
+      <c r="K77">
+        <v>26.44</v>
+      </c>
+      <c r="L77">
+        <v>28.56</v>
+      </c>
+      <c r="M77">
+        <v>53.82342</v>
+      </c>
+      <c r="N77">
+        <v>-25.26342</v>
+      </c>
+      <c r="O77">
+        <v>-6.315855</v>
+      </c>
+      <c r="P77">
+        <v>-18.947565</v>
+      </c>
+      <c r="Q77">
+        <v>7.492435</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="S77">
+        <v>0.270406801962104</v>
+      </c>
+      <c r="T77">
+        <v>4.228986414056461</v>
+      </c>
+      <c r="U77">
+        <v>0.2088</v>
+      </c>
+      <c r="V77">
+        <v>0.1326560073663101</v>
+      </c>
+      <c r="W77">
+        <v>0.1811014256619145</v>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y77">
+        <v>0.5306240294652402</v>
+      </c>
+      <c r="Z77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.76</v>
+      </c>
+      <c r="B78">
+        <v>0.2051277697369619</v>
+      </c>
+      <c r="C78">
+        <v>-100.7319948289448</v>
+      </c>
+      <c r="D78">
+        <v>103.2800051710552</v>
+      </c>
+      <c r="E78">
+        <v>169.112</v>
+      </c>
+      <c r="F78">
+        <v>261.212</v>
+      </c>
+      <c r="G78">
+        <v>57.2</v>
+      </c>
+      <c r="H78">
+        <v>251.6</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="J78">
+        <v>55</v>
+      </c>
+      <c r="K78">
+        <v>26.44</v>
+      </c>
+      <c r="L78">
+        <v>28.56</v>
+      </c>
+      <c r="M78">
+        <v>54.5410656</v>
+      </c>
+      <c r="N78">
+        <v>-25.9810656</v>
+      </c>
+      <c r="O78">
+        <v>-6.495266400000001</v>
+      </c>
+      <c r="P78">
+        <v>-19.4857992</v>
+      </c>
+      <c r="Q78">
+        <v>6.954200799999999</v>
+      </c>
+      <c r="R78">
+        <v>3.166666666666667</v>
+      </c>
+      <c r="S78">
+        <v>0.2800570853771918</v>
+      </c>
+      <c r="T78">
+        <v>4.405194181308815</v>
+      </c>
+      <c r="U78">
+        <v>0.2088</v>
+      </c>
+      <c r="V78">
+        <v>0.1309105335851744</v>
+      </c>
+      <c r="W78">
+        <v>0.1814658805874156</v>
+      </c>
+      <c r="X78" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y78">
+        <v>0.5236421343406976</v>
+      </c>
+      <c r="Z78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.77</v>
+      </c>
+      <c r="B79">
+        <v>0.2068277697369619</v>
+      </c>
+      <c r="C79">
+        <v>-105.2139173977895</v>
+      </c>
+      <c r="D79">
+        <v>102.2350826022105</v>
+      </c>
+      <c r="E79">
+        <v>172.549</v>
+      </c>
+      <c r="F79">
+        <v>264.649</v>
+      </c>
+      <c r="G79">
+        <v>57.2</v>
+      </c>
+      <c r="H79">
+        <v>251.6</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="J79">
+        <v>55</v>
+      </c>
+      <c r="K79">
+        <v>26.44</v>
+      </c>
+      <c r="L79">
+        <v>28.56</v>
+      </c>
+      <c r="M79">
+        <v>55.2587112</v>
+      </c>
+      <c r="N79">
+        <v>-26.6987112</v>
+      </c>
+      <c r="O79">
+        <v>-6.6746778</v>
+      </c>
+      <c r="P79">
+        <v>-20.0240334</v>
+      </c>
+      <c r="Q79">
+        <v>6.415966600000001</v>
+      </c>
+      <c r="R79">
+        <v>3.347826086956522</v>
+      </c>
+      <c r="S79">
+        <v>0.2905465238718523</v>
+      </c>
+      <c r="T79">
+        <v>4.59672436310485</v>
+      </c>
+      <c r="U79">
+        <v>0.2088</v>
+      </c>
+      <c r="V79">
+        <v>0.1292103967853669</v>
+      </c>
+      <c r="W79">
+        <v>0.1818208691512154</v>
+      </c>
+      <c r="X79" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y79">
+        <v>0.5168415871414678</v>
+      </c>
+      <c r="Z79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.78</v>
+      </c>
+      <c r="B80">
+        <v>0.2085277697369619</v>
+      </c>
+      <c r="C80">
+        <v>-109.6749079957518</v>
+      </c>
+      <c r="D80">
+        <v>101.2110920042482</v>
+      </c>
+      <c r="E80">
+        <v>175.986</v>
+      </c>
+      <c r="F80">
+        <v>268.086</v>
+      </c>
+      <c r="G80">
+        <v>57.2</v>
+      </c>
+      <c r="H80">
+        <v>251.6</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>55</v>
+      </c>
+      <c r="K80">
+        <v>26.44</v>
+      </c>
+      <c r="L80">
+        <v>28.56</v>
+      </c>
+      <c r="M80">
+        <v>55.9763568</v>
+      </c>
+      <c r="N80">
+        <v>-27.41635680000001</v>
+      </c>
+      <c r="O80">
+        <v>-6.854089200000002</v>
+      </c>
+      <c r="P80">
+        <v>-20.56226760000001</v>
+      </c>
+      <c r="Q80">
+        <v>5.877732399999996</v>
+      </c>
+      <c r="R80">
+        <v>3.545454545454546</v>
+      </c>
+      <c r="S80">
+        <v>0.3019895476842092</v>
+      </c>
+      <c r="T80">
+        <v>4.805666379609616</v>
+      </c>
+      <c r="U80">
+        <v>0.2088</v>
+      </c>
+      <c r="V80">
+        <v>0.1275538532368366</v>
+      </c>
+      <c r="W80">
+        <v>0.1821667554441485</v>
+      </c>
+      <c r="X80" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y80">
+        <v>0.5102154129473463</v>
+      </c>
+      <c r="Z80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.79</v>
+      </c>
+      <c r="B81">
+        <v>0.2102277697369619</v>
+      </c>
+      <c r="C81">
+        <v>-114.1155893518777</v>
+      </c>
+      <c r="D81">
+        <v>100.2074106481223</v>
+      </c>
+      <c r="E81">
+        <v>179.423</v>
+      </c>
+      <c r="F81">
+        <v>271.523</v>
+      </c>
+      <c r="G81">
+        <v>57.2</v>
+      </c>
+      <c r="H81">
+        <v>251.6</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>55</v>
+      </c>
+      <c r="K81">
+        <v>26.44</v>
+      </c>
+      <c r="L81">
+        <v>28.56</v>
+      </c>
+      <c r="M81">
+        <v>56.69400240000001</v>
+      </c>
+      <c r="N81">
+        <v>-28.13400240000001</v>
+      </c>
+      <c r="O81">
+        <v>-7.033500600000003</v>
+      </c>
+      <c r="P81">
+        <v>-21.10050180000001</v>
+      </c>
+      <c r="Q81">
+        <v>5.339498199999994</v>
+      </c>
+      <c r="R81">
+        <v>3.761904761904763</v>
+      </c>
+      <c r="S81">
+        <v>0.3145223832882191</v>
+      </c>
+      <c r="T81">
+        <v>5.034507635781503</v>
+      </c>
+      <c r="U81">
+        <v>0.2088</v>
+      </c>
+      <c r="V81">
+        <v>0.1259392474996614</v>
+      </c>
+      <c r="W81">
+        <v>0.1825038851220707</v>
+      </c>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>C2/C</t>
+        </is>
+      </c>
+      <c r="Y81">
+        <v>0.5037569899986456</v>
+      </c>
+      <c r="Z81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.8</v>
+      </c>
+      <c r="B82">
+        <v>0.2367314417844009</v>
+      </c>
+      <c r="C82">
+        <v>-130.9706917240809</v>
+      </c>
+      <c r="D82">
+        <v>86.78930827591911</v>
+      </c>
+      <c r="E82">
+        <v>182.86</v>
+      </c>
+      <c r="F82">
+        <v>274.96</v>
+      </c>
+      <c r="G82">
+        <v>57.2</v>
+      </c>
+      <c r="H82">
+        <v>251.6</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>55</v>
+      </c>
+      <c r="K82">
+        <v>26.44</v>
+      </c>
+      <c r="L82">
+        <v>28.56</v>
+      </c>
+      <c r="M82">
+        <v>65.660448</v>
+      </c>
+      <c r="N82">
+        <v>-37.100448</v>
+      </c>
+      <c r="O82">
+        <v>-9.275112</v>
+      </c>
+      <c r="P82">
+        <v>-27.825336</v>
+      </c>
+      <c r="Q82">
+        <v>-1.385335999999999</v>
+      </c>
+      <c r="R82">
+        <v>4.000000000000001</v>
+      </c>
+      <c r="S82">
+        <v>0.3323268626898251</v>
+      </c>
+      <c r="T82">
+        <v>5.359605607261026</v>
+      </c>
+      <c r="U82">
+        <v>0.2388</v>
+      </c>
+      <c r="V82">
+        <v>0.1087412623197454</v>
+      </c>
+      <c r="W82">
+        <v>0.2128325865580448</v>
+      </c>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y82">
+        <v>0.4349650492789815</v>
+      </c>
+      <c r="Z82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8100000000000001</v>
+      </c>
+      <c r="B83">
+        <v>0.2387314417844009</v>
+      </c>
+      <c r="C83">
+        <v>-135.2758824148629</v>
+      </c>
+      <c r="D83">
+        <v>85.9211175851371</v>
+      </c>
+      <c r="E83">
+        <v>186.297</v>
+      </c>
+      <c r="F83">
+        <v>278.397</v>
+      </c>
+      <c r="G83">
+        <v>57.2</v>
+      </c>
+      <c r="H83">
+        <v>251.6</v>
+      </c>
+      <c r="I83">
+        <v>0</v>
+      </c>
+      <c r="J83">
+        <v>55</v>
+      </c>
+      <c r="K83">
+        <v>26.44</v>
+      </c>
+      <c r="L83">
+        <v>28.56</v>
+      </c>
+      <c r="M83">
+        <v>66.4812036</v>
+      </c>
+      <c r="N83">
+        <v>-37.9212036</v>
+      </c>
+      <c r="O83">
+        <v>-9.4803009</v>
+      </c>
+      <c r="P83">
+        <v>-28.4409027</v>
+      </c>
+      <c r="Q83">
+        <v>-2.000902699999997</v>
+      </c>
+      <c r="R83">
+        <v>4.263157894736843</v>
+      </c>
+      <c r="S83">
+        <v>0.347775644936658</v>
+      </c>
+      <c r="T83">
+        <v>5.641690112906344</v>
+      </c>
+      <c r="U83">
+        <v>0.2388</v>
+      </c>
+      <c r="V83">
+        <v>0.1073987775997485</v>
+      </c>
+      <c r="W83">
+        <v>0.2131531719091801</v>
+      </c>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y83">
+        <v>0.4295951103989941</v>
+      </c>
+      <c r="Z83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.8200000000000001</v>
+      </c>
+      <c r="B84">
+        <v>0.2407314417844009</v>
+      </c>
+      <c r="C84">
+        <v>-139.5638753739175</v>
+      </c>
+      <c r="D84">
+        <v>85.07012462608247</v>
+      </c>
+      <c r="E84">
+        <v>189.734</v>
+      </c>
+      <c r="F84">
+        <v>281.834</v>
+      </c>
+      <c r="G84">
+        <v>57.2</v>
+      </c>
+      <c r="H84">
+        <v>251.6</v>
+      </c>
+      <c r="I84">
+        <v>0</v>
+      </c>
+      <c r="J84">
+        <v>55</v>
+      </c>
+      <c r="K84">
+        <v>26.44</v>
+      </c>
+      <c r="L84">
+        <v>28.56</v>
+      </c>
+      <c r="M84">
+        <v>67.3019592</v>
+      </c>
+      <c r="N84">
+        <v>-38.7419592</v>
+      </c>
+      <c r="O84">
+        <v>-9.685489799999999</v>
+      </c>
+      <c r="P84">
+        <v>-29.0564694</v>
+      </c>
+      <c r="Q84">
+        <v>-2.616469399999996</v>
+      </c>
+      <c r="R84">
+        <v>4.555555555555557</v>
+      </c>
+      <c r="S84">
+        <v>0.3649409585442501</v>
+      </c>
+      <c r="T84">
+        <v>5.955117341401141</v>
+      </c>
+      <c r="U84">
+        <v>0.2388</v>
+      </c>
+      <c r="V84">
+        <v>0.1060890364095077</v>
+      </c>
+      <c r="W84">
+        <v>0.2134659381054096</v>
+      </c>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y84">
+        <v>0.4243561456380307</v>
+      </c>
+      <c r="Z84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.8300000000000001</v>
+      </c>
+      <c r="B85">
+        <v>0.2427314417844009</v>
+      </c>
+      <c r="C85">
+        <v>-143.8351765869303</v>
+      </c>
+      <c r="D85">
+        <v>84.23582341306974</v>
+      </c>
+      <c r="E85">
+        <v>193.171</v>
+      </c>
+      <c r="F85">
+        <v>285.271</v>
+      </c>
+      <c r="G85">
+        <v>57.2</v>
+      </c>
+      <c r="H85">
+        <v>251.6</v>
+      </c>
+      <c r="I85">
+        <v>0</v>
+      </c>
+      <c r="J85">
+        <v>55</v>
+      </c>
+      <c r="K85">
+        <v>26.44</v>
+      </c>
+      <c r="L85">
+        <v>28.56</v>
+      </c>
+      <c r="M85">
+        <v>68.12271480000001</v>
+      </c>
+      <c r="N85">
+        <v>-39.56271480000001</v>
+      </c>
+      <c r="O85">
+        <v>-9.890678700000002</v>
+      </c>
+      <c r="P85">
+        <v>-29.67203610000001</v>
+      </c>
+      <c r="Q85">
+        <v>-3.232036100000006</v>
+      </c>
+      <c r="R85">
+        <v>4.882352941176473</v>
+      </c>
+      <c r="S85">
+        <v>0.384125720811559</v>
+      </c>
+      <c r="T85">
+        <v>6.305418361483563</v>
+      </c>
+      <c r="U85">
+        <v>0.2388</v>
+      </c>
+      <c r="V85">
+        <v>0.1048108552479473</v>
+      </c>
+      <c r="W85">
+        <v>0.2137711677667902</v>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y85">
+        <v>0.4192434209917894</v>
+      </c>
+      <c r="Z85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.84</v>
+      </c>
+      <c r="B86">
+        <v>0.2447314417844009</v>
+      </c>
+      <c r="C86">
+        <v>-148.0902723831153</v>
+      </c>
+      <c r="D86">
+        <v>83.4177276168847</v>
+      </c>
+      <c r="E86">
+        <v>196.608</v>
+      </c>
+      <c r="F86">
+        <v>288.708</v>
+      </c>
+      <c r="G86">
+        <v>57.2</v>
+      </c>
+      <c r="H86">
+        <v>251.6</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>55</v>
+      </c>
+      <c r="K86">
+        <v>26.44</v>
+      </c>
+      <c r="L86">
+        <v>28.56</v>
+      </c>
+      <c r="M86">
+        <v>68.9434704</v>
+      </c>
+      <c r="N86">
+        <v>-40.38347039999999</v>
+      </c>
+      <c r="O86">
+        <v>-10.0958676</v>
+      </c>
+      <c r="P86">
+        <v>-30.28760279999999</v>
+      </c>
+      <c r="Q86">
+        <v>-3.847602799999994</v>
+      </c>
+      <c r="R86">
+        <v>5.249999999999999</v>
+      </c>
+      <c r="S86">
+        <v>0.4057085783622812</v>
+      </c>
+      <c r="T86">
+        <v>6.699507009076281</v>
+      </c>
+      <c r="U86">
+        <v>0.2388</v>
+      </c>
+      <c r="V86">
+        <v>0.1035631069711861</v>
+      </c>
+      <c r="W86">
+        <v>0.2140691300552808</v>
+      </c>
+      <c r="X86" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y86">
+        <v>0.4142524278847444</v>
+      </c>
+      <c r="Z86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>0.85</v>
+      </c>
+      <c r="B87">
+        <v>0.2467314417844009</v>
+      </c>
+      <c r="C87">
+        <v>-152.3296303805496</v>
+      </c>
+      <c r="D87">
+        <v>82.61536961945035</v>
+      </c>
+      <c r="E87">
+        <v>200.045</v>
+      </c>
+      <c r="F87">
+        <v>292.145</v>
+      </c>
+      <c r="G87">
+        <v>57.2</v>
+      </c>
+      <c r="H87">
+        <v>251.6</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>55</v>
+      </c>
+      <c r="K87">
+        <v>26.44</v>
+      </c>
+      <c r="L87">
+        <v>28.56</v>
+      </c>
+      <c r="M87">
+        <v>69.76422599999999</v>
+      </c>
+      <c r="N87">
+        <v>-41.20422599999999</v>
+      </c>
+      <c r="O87">
+        <v>-10.3010565</v>
+      </c>
+      <c r="P87">
+        <v>-30.90316949999999</v>
+      </c>
+      <c r="Q87">
+        <v>-4.463169499999992</v>
+      </c>
+      <c r="R87">
+        <v>5.666666666666666</v>
+      </c>
+      <c r="S87">
+        <v>0.4301691502531</v>
+      </c>
+      <c r="T87">
+        <v>7.146140809681366</v>
+      </c>
+      <c r="U87">
+        <v>0.2388</v>
+      </c>
+      <c r="V87">
+        <v>0.1023447174774074</v>
+      </c>
+      <c r="W87">
+        <v>0.2143600814663951</v>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y87">
+        <v>0.4093788699096297</v>
+      </c>
+      <c r="Z87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.86</v>
+      </c>
+      <c r="B88">
+        <v>0.2487314417844008</v>
+      </c>
+      <c r="C88">
+        <v>-156.5537003774708</v>
+      </c>
+      <c r="D88">
+        <v>81.82829962252916</v>
+      </c>
+      <c r="E88">
+        <v>203.482</v>
+      </c>
+      <c r="F88">
+        <v>295.582</v>
+      </c>
+      <c r="G88">
+        <v>57.2</v>
+      </c>
+      <c r="H88">
+        <v>251.6</v>
+      </c>
+      <c r="I88">
+        <v>0</v>
+      </c>
+      <c r="J88">
+        <v>55</v>
+      </c>
+      <c r="K88">
+        <v>26.44</v>
+      </c>
+      <c r="L88">
+        <v>28.56</v>
+      </c>
+      <c r="M88">
+        <v>70.58498160000001</v>
+      </c>
+      <c r="N88">
+        <v>-42.0249816</v>
+      </c>
+      <c r="O88">
+        <v>-10.5062454</v>
+      </c>
+      <c r="P88">
+        <v>-31.5187362</v>
+      </c>
+      <c r="Q88">
+        <v>-5.078736200000002</v>
+      </c>
+      <c r="R88">
+        <v>6.142857142857142</v>
+      </c>
+      <c r="S88">
+        <v>0.4581240895568929</v>
+      </c>
+      <c r="T88">
+        <v>7.656579438944321</v>
+      </c>
+      <c r="U88">
+        <v>0.2388</v>
+      </c>
+      <c r="V88">
+        <v>0.1011546626230189</v>
+      </c>
+      <c r="W88">
+        <v>0.2146442665656231</v>
+      </c>
+      <c r="X88" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y88">
+        <v>0.4046186504920758</v>
+      </c>
+      <c r="Z88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>0.87</v>
+      </c>
+      <c r="B89">
+        <v>0.2507314417844009</v>
+      </c>
+      <c r="C89">
+        <v>-160.762915193107</v>
+      </c>
+      <c r="D89">
+        <v>81.05608480689298</v>
+      </c>
+      <c r="E89">
+        <v>206.919</v>
+      </c>
+      <c r="F89">
+        <v>299.019</v>
+      </c>
+      <c r="G89">
+        <v>57.2</v>
+      </c>
+      <c r="H89">
+        <v>251.6</v>
+      </c>
+      <c r="I89">
+        <v>0</v>
+      </c>
+      <c r="J89">
+        <v>55</v>
+      </c>
+      <c r="K89">
+        <v>26.44</v>
+      </c>
+      <c r="L89">
+        <v>28.56</v>
+      </c>
+      <c r="M89">
+        <v>71.4057372</v>
+      </c>
+      <c r="N89">
+        <v>-42.8457372</v>
+      </c>
+      <c r="O89">
+        <v>-10.7114343</v>
+      </c>
+      <c r="P89">
+        <v>-32.1343029</v>
+      </c>
+      <c r="Q89">
+        <v>-5.6943029</v>
+      </c>
+      <c r="R89">
+        <v>6.692307692307692</v>
+      </c>
+      <c r="S89">
+        <v>0.490379788753577</v>
+      </c>
+      <c r="T89">
+        <v>8.245547088093884</v>
+      </c>
+      <c r="U89">
+        <v>0.2388</v>
+      </c>
+      <c r="V89">
+        <v>0.09999196535148998</v>
+      </c>
+      <c r="W89">
+        <v>0.2149219186740642</v>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y89">
+        <v>0.39996786140596</v>
+      </c>
+      <c r="Z89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>0.88</v>
+      </c>
+      <c r="B90">
+        <v>0.2527314417844009</v>
+      </c>
+      <c r="C90">
+        <v>-164.9576914613433</v>
+      </c>
+      <c r="D90">
+        <v>80.29830853865673</v>
+      </c>
+      <c r="E90">
+        <v>210.356</v>
+      </c>
+      <c r="F90">
+        <v>302.456</v>
+      </c>
+      <c r="G90">
+        <v>57.2</v>
+      </c>
+      <c r="H90">
+        <v>251.6</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>55</v>
+      </c>
+      <c r="K90">
+        <v>26.44</v>
+      </c>
+      <c r="L90">
+        <v>28.56</v>
+      </c>
+      <c r="M90">
+        <v>72.2264928</v>
+      </c>
+      <c r="N90">
+        <v>-43.6664928</v>
+      </c>
+      <c r="O90">
+        <v>-10.9166232</v>
+      </c>
+      <c r="P90">
+        <v>-32.7498696</v>
+      </c>
+      <c r="Q90">
+        <v>-6.309869599999995</v>
+      </c>
+      <c r="R90">
+        <v>7.333333333333334</v>
+      </c>
+      <c r="S90">
+        <v>0.5280114378163752</v>
+      </c>
+      <c r="T90">
+        <v>8.932676012101711</v>
+      </c>
+      <c r="U90">
+        <v>0.2388</v>
+      </c>
+      <c r="V90">
+        <v>0.09885569301795033</v>
+      </c>
+      <c r="W90">
+        <v>0.2151932605073135</v>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y90">
+        <v>0.3954227720718013</v>
+      </c>
+      <c r="Z90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>0.89</v>
+      </c>
+      <c r="B91">
+        <v>0.2547314417844009</v>
+      </c>
+      <c r="C91">
+        <v>-169.1384303802806</v>
+      </c>
+      <c r="D91">
+        <v>79.55456961971937</v>
+      </c>
+      <c r="E91">
+        <v>213.793</v>
+      </c>
+      <c r="F91">
+        <v>305.893</v>
+      </c>
+      <c r="G91">
+        <v>57.2</v>
+      </c>
+      <c r="H91">
+        <v>251.6</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>55</v>
+      </c>
+      <c r="K91">
+        <v>26.44</v>
+      </c>
+      <c r="L91">
+        <v>28.56</v>
+      </c>
+      <c r="M91">
+        <v>73.0472484</v>
+      </c>
+      <c r="N91">
+        <v>-44.4872484</v>
+      </c>
+      <c r="O91">
+        <v>-11.1218121</v>
+      </c>
+      <c r="P91">
+        <v>-33.3654363</v>
+      </c>
+      <c r="Q91">
+        <v>-6.925436299999998</v>
+      </c>
+      <c r="R91">
+        <v>8.090909090909092</v>
+      </c>
+      <c r="S91">
+        <v>0.5724852048905911</v>
+      </c>
+      <c r="T91">
+        <v>9.744737467747321</v>
+      </c>
+      <c r="U91">
+        <v>0.2388</v>
+      </c>
+      <c r="V91">
+        <v>0.09774495489415314</v>
+      </c>
+      <c r="W91">
+        <v>0.2154585047712762</v>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y91">
+        <v>0.3909798195766125</v>
+      </c>
+      <c r="Z91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>0.9</v>
+      </c>
+      <c r="B92">
+        <v>0.2567314417844008</v>
+      </c>
+      <c r="C92">
+        <v>-173.3055184205224</v>
+      </c>
+      <c r="D92">
+        <v>78.82448157947761</v>
+      </c>
+      <c r="E92">
+        <v>217.23</v>
+      </c>
+      <c r="F92">
+        <v>309.33</v>
+      </c>
+      <c r="G92">
+        <v>57.2</v>
+      </c>
+      <c r="H92">
+        <v>251.6</v>
+      </c>
+      <c r="I92">
+        <v>0</v>
+      </c>
+      <c r="J92">
+        <v>55</v>
+      </c>
+      <c r="K92">
+        <v>26.44</v>
+      </c>
+      <c r="L92">
+        <v>28.56</v>
+      </c>
+      <c r="M92">
+        <v>73.868004</v>
+      </c>
+      <c r="N92">
+        <v>-45.308004</v>
+      </c>
+      <c r="O92">
+        <v>-11.327001</v>
+      </c>
+      <c r="P92">
+        <v>-33.981003</v>
+      </c>
+      <c r="Q92">
+        <v>-7.541003</v>
+      </c>
+      <c r="R92">
+        <v>9.000000000000002</v>
+      </c>
+      <c r="S92">
+        <v>0.6258537253796501</v>
+      </c>
+      <c r="T92">
+        <v>10.71921121452205</v>
+      </c>
+      <c r="U92">
+        <v>0.2388</v>
+      </c>
+      <c r="V92">
+        <v>0.09665889983977366</v>
+      </c>
+      <c r="W92">
+        <v>0.215717854718262</v>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y92">
+        <v>0.3866355993590946</v>
+      </c>
+      <c r="Z92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>0.91</v>
+      </c>
+      <c r="B93">
+        <v>0.2587314417844009</v>
+      </c>
+      <c r="C93">
+        <v>-177.4593279948146</v>
+      </c>
+      <c r="D93">
+        <v>78.10767200518536</v>
+      </c>
+      <c r="E93">
+        <v>220.667</v>
+      </c>
+      <c r="F93">
+        <v>312.767</v>
+      </c>
+      <c r="G93">
+        <v>57.2</v>
+      </c>
+      <c r="H93">
+        <v>251.6</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>55</v>
+      </c>
+      <c r="K93">
+        <v>26.44</v>
+      </c>
+      <c r="L93">
+        <v>28.56</v>
+      </c>
+      <c r="M93">
+        <v>74.6887596</v>
+      </c>
+      <c r="N93">
+        <v>-46.1287596</v>
+      </c>
+      <c r="O93">
+        <v>-11.5321899</v>
+      </c>
+      <c r="P93">
+        <v>-34.5965697</v>
+      </c>
+      <c r="Q93">
+        <v>-8.156569699999995</v>
+      </c>
+      <c r="R93">
+        <v>10.11111111111111</v>
+      </c>
+      <c r="S93">
+        <v>0.6910819170885003</v>
+      </c>
+      <c r="T93">
+        <v>11.91023468280228</v>
+      </c>
+      <c r="U93">
+        <v>0.2388</v>
+      </c>
+      <c r="V93">
+        <v>0.09559671412724867</v>
+      </c>
+      <c r="W93">
+        <v>0.215971504666413</v>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y93">
+        <v>0.3823868565089947</v>
+      </c>
+      <c r="Z93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>0.92</v>
+      </c>
+      <c r="B94">
+        <v>0.2607314417844009</v>
+      </c>
+      <c r="C94">
+        <v>-181.6002180914785</v>
+      </c>
+      <c r="D94">
+        <v>77.40378190852151</v>
+      </c>
+      <c r="E94">
+        <v>224.104</v>
+      </c>
+      <c r="F94">
+        <v>316.204</v>
+      </c>
+      <c r="G94">
+        <v>57.2</v>
+      </c>
+      <c r="H94">
+        <v>251.6</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>55</v>
+      </c>
+      <c r="K94">
+        <v>26.44</v>
+      </c>
+      <c r="L94">
+        <v>28.56</v>
+      </c>
+      <c r="M94">
+        <v>75.50951520000001</v>
+      </c>
+      <c r="N94">
+        <v>-46.94951520000001</v>
+      </c>
+      <c r="O94">
+        <v>-11.7373788</v>
+      </c>
+      <c r="P94">
+        <v>-35.21213640000001</v>
+      </c>
+      <c r="Q94">
+        <v>-8.772136400000004</v>
+      </c>
+      <c r="R94">
+        <v>11.50000000000001</v>
+      </c>
+      <c r="S94">
+        <v>0.772617156724563</v>
+      </c>
+      <c r="T94">
+        <v>13.39901401815257</v>
+      </c>
+      <c r="U94">
+        <v>0.2388</v>
+      </c>
+      <c r="V94">
+        <v>0.09455761940847421</v>
+      </c>
+      <c r="W94">
+        <v>0.2162196404852564</v>
+      </c>
+      <c r="X94" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y94">
+        <v>0.3782304776338969</v>
+      </c>
+      <c r="Z94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>0.93</v>
+      </c>
+      <c r="B95">
+        <v>0.2627314417844009</v>
+      </c>
+      <c r="C95">
+        <v>-185.7285348738984</v>
+      </c>
+      <c r="D95">
+        <v>76.71246512610158</v>
+      </c>
+      <c r="E95">
+        <v>227.541</v>
+      </c>
+      <c r="F95">
+        <v>319.641</v>
+      </c>
+      <c r="G95">
+        <v>57.2</v>
+      </c>
+      <c r="H95">
+        <v>251.6</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>55</v>
+      </c>
+      <c r="K95">
+        <v>26.44</v>
+      </c>
+      <c r="L95">
+        <v>28.56</v>
+      </c>
+      <c r="M95">
+        <v>76.33027080000001</v>
+      </c>
+      <c r="N95">
+        <v>-47.77027080000001</v>
+      </c>
+      <c r="O95">
+        <v>-11.9425677</v>
+      </c>
+      <c r="P95">
+        <v>-35.82770310000001</v>
+      </c>
+      <c r="Q95">
+        <v>-9.387703100000007</v>
+      </c>
+      <c r="R95">
+        <v>13.2857142857143</v>
+      </c>
+      <c r="S95">
+        <v>0.8774481791137865</v>
+      </c>
+      <c r="T95">
+        <v>15.31315887788865</v>
+      </c>
+      <c r="U95">
+        <v>0.2388</v>
+      </c>
+      <c r="V95">
+        <v>0.09354087081268417</v>
+      </c>
+      <c r="W95">
+        <v>0.216462440049931</v>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y95">
+        <v>0.3741634832507368</v>
+      </c>
+      <c r="Z95">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>0.9400000000000001</v>
+      </c>
+      <c r="B96">
+        <v>0.2647314417844009</v>
+      </c>
+      <c r="C96">
+        <v>-189.8446122481694</v>
+      </c>
+      <c r="D96">
+        <v>76.03338775183063</v>
+      </c>
+      <c r="E96">
+        <v>230.978</v>
+      </c>
+      <c r="F96">
+        <v>323.078</v>
+      </c>
+      <c r="G96">
+        <v>57.2</v>
+      </c>
+      <c r="H96">
+        <v>251.6</v>
+      </c>
+      <c r="I96">
+        <v>0</v>
+      </c>
+      <c r="J96">
+        <v>55</v>
+      </c>
+      <c r="K96">
+        <v>26.44</v>
+      </c>
+      <c r="L96">
+        <v>28.56</v>
+      </c>
+      <c r="M96">
+        <v>77.15102640000001</v>
+      </c>
+      <c r="N96">
+        <v>-48.5910264</v>
+      </c>
+      <c r="O96">
+        <v>-12.1477566</v>
+      </c>
+      <c r="P96">
+        <v>-36.4432698</v>
+      </c>
+      <c r="Q96">
+        <v>-10.0032698</v>
+      </c>
+      <c r="R96">
+        <v>15.66666666666668</v>
+      </c>
+      <c r="S96">
+        <v>1.017222875632751</v>
+      </c>
+      <c r="T96">
+        <v>17.86535202420344</v>
+      </c>
+      <c r="U96">
+        <v>0.2388</v>
+      </c>
+      <c r="V96">
+        <v>0.09254575516574072</v>
+      </c>
+      <c r="W96">
+        <v>0.2167000736664211</v>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y96">
+        <v>0.3701830206629629</v>
+      </c>
+      <c r="Z96">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>0.9500000000000001</v>
+      </c>
+      <c r="B97">
+        <v>0.2667314417844009</v>
+      </c>
+      <c r="C97">
+        <v>-193.948772400859</v>
+      </c>
+      <c r="D97">
+        <v>75.36622759914096</v>
+      </c>
+      <c r="E97">
+        <v>234.415</v>
+      </c>
+      <c r="F97">
+        <v>326.515</v>
+      </c>
+      <c r="G97">
+        <v>57.2</v>
+      </c>
+      <c r="H97">
+        <v>251.6</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>55</v>
+      </c>
+      <c r="K97">
+        <v>26.44</v>
+      </c>
+      <c r="L97">
+        <v>28.56</v>
+      </c>
+      <c r="M97">
+        <v>77.971782</v>
+      </c>
+      <c r="N97">
+        <v>-49.411782</v>
+      </c>
+      <c r="O97">
+        <v>-12.3529455</v>
+      </c>
+      <c r="P97">
+        <v>-37.0588365</v>
+      </c>
+      <c r="Q97">
+        <v>-10.6188365</v>
+      </c>
+      <c r="R97">
+        <v>19.00000000000003</v>
+      </c>
+      <c r="S97">
+        <v>1.212907450759302</v>
+      </c>
+      <c r="T97">
+        <v>21.43842242904413</v>
+      </c>
+      <c r="U97">
+        <v>0.2388</v>
+      </c>
+      <c r="V97">
+        <v>0.09157158932189083</v>
+      </c>
+      <c r="W97">
+        <v>0.2169327044699325</v>
+      </c>
+      <c r="X97" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y97">
+        <v>0.3662863572875633</v>
+      </c>
+      <c r="Z97">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>0.96</v>
+      </c>
+      <c r="B98">
+        <v>0.2687314417844009</v>
+      </c>
+      <c r="C98">
+        <v>-198.0413263087044</v>
+      </c>
+      <c r="D98">
+        <v>74.71067369129557</v>
+      </c>
+      <c r="E98">
+        <v>237.852</v>
+      </c>
+      <c r="F98">
+        <v>329.952</v>
+      </c>
+      <c r="G98">
+        <v>57.2</v>
+      </c>
+      <c r="H98">
+        <v>251.6</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>55</v>
+      </c>
+      <c r="K98">
+        <v>26.44</v>
+      </c>
+      <c r="L98">
+        <v>28.56</v>
+      </c>
+      <c r="M98">
+        <v>78.7925376</v>
+      </c>
+      <c r="N98">
+        <v>-50.2325376</v>
+      </c>
+      <c r="O98">
+        <v>-12.5581344</v>
+      </c>
+      <c r="P98">
+        <v>-37.6744032</v>
+      </c>
+      <c r="Q98">
+        <v>-11.2344032</v>
+      </c>
+      <c r="R98">
+        <v>23.99999999999998</v>
+      </c>
+      <c r="S98">
+        <v>1.506434313449124</v>
+      </c>
+      <c r="T98">
+        <v>26.7980280363051</v>
+      </c>
+      <c r="U98">
+        <v>0.2388</v>
+      </c>
+      <c r="V98">
+        <v>0.0906177185997878</v>
+      </c>
+      <c r="W98">
+        <v>0.2171604887983707</v>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y98">
+        <v>0.3624708743991513</v>
+      </c>
+      <c r="Z98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>0.97</v>
+      </c>
+      <c r="B99">
+        <v>0.2707314417844008</v>
+      </c>
+      <c r="C99">
+        <v>-202.1225742219368</v>
+      </c>
+      <c r="D99">
+        <v>74.06642577806315</v>
+      </c>
+      <c r="E99">
+        <v>241.289</v>
+      </c>
+      <c r="F99">
+        <v>333.389</v>
+      </c>
+      <c r="G99">
+        <v>57.2</v>
+      </c>
+      <c r="H99">
+        <v>251.6</v>
+      </c>
+      <c r="I99">
+        <v>0</v>
+      </c>
+      <c r="J99">
+        <v>55</v>
+      </c>
+      <c r="K99">
+        <v>26.44</v>
+      </c>
+      <c r="L99">
+        <v>28.56</v>
+      </c>
+      <c r="M99">
+        <v>79.61329319999999</v>
+      </c>
+      <c r="N99">
+        <v>-51.05329319999998</v>
+      </c>
+      <c r="O99">
+        <v>-12.7633233</v>
+      </c>
+      <c r="P99">
+        <v>-38.28996989999999</v>
+      </c>
+      <c r="Q99">
+        <v>-11.84996989999999</v>
+      </c>
+      <c r="R99">
+        <v>32.33333333333331</v>
+      </c>
+      <c r="S99">
+        <v>1.995645751265499</v>
+      </c>
+      <c r="T99">
+        <v>35.73070404840681</v>
+      </c>
+      <c r="U99">
+        <v>0.2388</v>
+      </c>
+      <c r="V99">
+        <v>0.08968351531525393</v>
+      </c>
+      <c r="W99">
+        <v>0.2173835765427174</v>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y99">
+        <v>0.3587340612610157</v>
+      </c>
+      <c r="Z99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>0.98</v>
+      </c>
+      <c r="B100">
+        <v>0.2727314417844009</v>
+      </c>
+      <c r="C100">
+        <v>-206.1928061228142</v>
+      </c>
+      <c r="D100">
+        <v>73.43319387718574</v>
+      </c>
+      <c r="E100">
+        <v>244.726</v>
+      </c>
+      <c r="F100">
+        <v>336.826</v>
+      </c>
+      <c r="G100">
+        <v>57.2</v>
+      </c>
+      <c r="H100">
+        <v>251.6</v>
+      </c>
+      <c r="I100">
+        <v>0</v>
+      </c>
+      <c r="J100">
+        <v>55</v>
+      </c>
+      <c r="K100">
+        <v>26.44</v>
+      </c>
+      <c r="L100">
+        <v>28.56</v>
+      </c>
+      <c r="M100">
+        <v>80.4340488</v>
+      </c>
+      <c r="N100">
+        <v>-51.8740488</v>
+      </c>
+      <c r="O100">
+        <v>-12.9685122</v>
+      </c>
+      <c r="P100">
+        <v>-38.9055366</v>
+      </c>
+      <c r="Q100">
+        <v>-12.4655366</v>
+      </c>
+      <c r="R100">
+        <v>48.99999999999996</v>
+      </c>
+      <c r="S100">
+        <v>2.974068626898248</v>
+      </c>
+      <c r="T100">
+        <v>53.5960560726102</v>
+      </c>
+      <c r="U100">
+        <v>0.2388</v>
+      </c>
+      <c r="V100">
+        <v>0.08876837740387376</v>
+      </c>
+      <c r="W100">
+        <v>0.217602111475955</v>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y100">
+        <v>0.3550735096154951</v>
+      </c>
+      <c r="Z100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>0.99</v>
+      </c>
+      <c r="B101">
+        <v>0.2747314417844009</v>
+      </c>
+      <c r="C101">
+        <v>-210.252302160831</v>
+      </c>
+      <c r="D101">
+        <v>72.81069783916898</v>
+      </c>
+      <c r="E101">
+        <v>248.163</v>
+      </c>
+      <c r="F101">
+        <v>340.263</v>
+      </c>
+      <c r="G101">
+        <v>57.2</v>
+      </c>
+      <c r="H101">
+        <v>251.6</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>55</v>
+      </c>
+      <c r="K101">
+        <v>26.44</v>
+      </c>
+      <c r="L101">
+        <v>28.56</v>
+      </c>
+      <c r="M101">
+        <v>81.2548044</v>
+      </c>
+      <c r="N101">
+        <v>-52.6948044</v>
+      </c>
+      <c r="O101">
+        <v>-13.1737011</v>
+      </c>
+      <c r="P101">
+        <v>-39.52110329999999</v>
+      </c>
+      <c r="Q101">
+        <v>-13.08110329999999</v>
+      </c>
+      <c r="R101">
+        <v>98.99999999999991</v>
+      </c>
+      <c r="S101">
+        <v>5.909337253796497</v>
+      </c>
+      <c r="T101">
+        <v>107.1921121452204</v>
+      </c>
+      <c r="U101">
+        <v>0.2388</v>
+      </c>
+      <c r="V101">
+        <v>0.08787172712706696</v>
+      </c>
+      <c r="W101">
+        <v>0.2178162315620564</v>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>D2/D</t>
+        </is>
+      </c>
+      <c r="Y101">
+        <v>0.3514869085082679</v>
+      </c>
+      <c r="Z101">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
